--- a/Solver.xlsx
+++ b/Solver.xlsx
@@ -21,11 +21,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="$#,##0"/>
+    <numFmt numFmtId="166" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -102,8 +103,40 @@
       <color rgb="002E75B6"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00AAAAAA"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -148,6 +181,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F0F8F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
   </fills>
@@ -221,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -350,6 +388,85 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3936,20 +4053,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q505"/>
+  <dimension ref="A1:S505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
@@ -3959,1668 +4076,1347 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>ALLOCATION RESULTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Last run: 2026-04-12  19:56   |   ✓  All checks passed   |   12 mech + 12 opt = 24 tooling sets</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="6" customHeight="1"/>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ALLOCATION TABLE  —  one row per active (year, line) pair</t>
-        </is>
-      </c>
+      <c r="A1" s="54" t="inlineStr">
+        <is>
+          <t>ALLOCATION  —  solver_ilp output</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+      <c r="D1" s="24" t="n"/>
+      <c r="E1" s="24" t="n"/>
+      <c r="F1" s="24" t="n"/>
+      <c r="G1" s="24" t="n"/>
+      <c r="H1" s="24" t="n"/>
+      <c r="I1" s="24" t="n"/>
+      <c r="J1" s="24" t="n"/>
+      <c r="K1" s="24" t="n"/>
+      <c r="L1" s="25" t="n"/>
+      <c r="M1" s="44" t="n"/>
+      <c r="N1" s="44" t="n"/>
+      <c r="O1" s="44" t="n"/>
+      <c r="P1" s="44" t="n"/>
+      <c r="Q1" s="44" t="n"/>
+      <c r="R1" s="44" t="n"/>
+      <c r="S1" s="44" t="n"/>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="55" t="inlineStr">
+        <is>
+          <t>Last run: 2026-04-13  07:22   |   ✓  All checks passed   |   7 lines used   |   12 mech + 12 opt = 24 tooling sets</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="n"/>
+      <c r="C2" s="24" t="n"/>
+      <c r="D2" s="24" t="n"/>
+      <c r="E2" s="24" t="n"/>
+      <c r="F2" s="24" t="n"/>
+      <c r="G2" s="24" t="n"/>
+      <c r="H2" s="24" t="n"/>
+      <c r="I2" s="24" t="n"/>
+      <c r="J2" s="24" t="n"/>
+      <c r="K2" s="24" t="n"/>
+      <c r="L2" s="25" t="n"/>
+      <c r="M2" s="44" t="n"/>
+      <c r="N2" s="44" t="n"/>
+      <c r="O2" s="44" t="n"/>
+      <c r="P2" s="44" t="n"/>
+      <c r="Q2" s="44" t="n"/>
+      <c r="R2" s="44" t="n"/>
+      <c r="S2" s="44" t="n"/>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="A3" s="44" t="n"/>
+      <c r="B3" s="44" t="n"/>
+      <c r="C3" s="44" t="n"/>
+      <c r="D3" s="44" t="n"/>
+      <c r="E3" s="44" t="n"/>
+      <c r="F3" s="44" t="n"/>
+      <c r="G3" s="44" t="n"/>
+      <c r="H3" s="44" t="n"/>
+      <c r="I3" s="44" t="n"/>
+      <c r="J3" s="44" t="n"/>
+      <c r="K3" s="44" t="n"/>
+      <c r="L3" s="44" t="n"/>
+      <c r="M3" s="44" t="n"/>
+      <c r="N3" s="44" t="n"/>
+      <c r="O3" s="44" t="n"/>
+      <c r="P3" s="44" t="n"/>
+      <c r="Q3" s="44" t="n"/>
+      <c r="R3" s="44" t="n"/>
+      <c r="S3" s="44" t="n"/>
+    </row>
+    <row r="4" ht="6" customHeight="1">
+      <c r="A4" s="56" t="n"/>
+      <c r="B4" s="44" t="n"/>
+      <c r="C4" s="44" t="n"/>
+      <c r="D4" s="44" t="n"/>
+      <c r="E4" s="44" t="n"/>
+      <c r="F4" s="44" t="n"/>
+      <c r="G4" s="44" t="n"/>
+      <c r="H4" s="44" t="n"/>
+      <c r="I4" s="44" t="n"/>
+      <c r="J4" s="44" t="n"/>
+      <c r="K4" s="44" t="n"/>
+      <c r="L4" s="44" t="n"/>
+      <c r="M4" s="44" t="n"/>
+      <c r="N4" s="44" t="n"/>
+      <c r="O4" s="44" t="n"/>
+      <c r="P4" s="44" t="n"/>
+      <c r="Q4" s="44" t="n"/>
+      <c r="R4" s="44" t="n"/>
+      <c r="S4" s="44" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="57" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>Products</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="B5" s="57" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C5" s="57" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D5" s="57" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="E5" s="57" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="F5" s="57" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="G5" s="57" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="H5" s="57" t="inlineStr">
+        <is>
+          <t>L14</t>
+        </is>
+      </c>
+      <c r="I5" s="57" t="inlineStr">
+        <is>
+          <t>Open
+Lines</t>
+        </is>
+      </c>
+      <c r="J5" s="57" t="inlineStr">
+        <is>
+          <t>Total
+Demand</t>
+        </is>
+      </c>
+      <c r="K5" s="57" t="inlineStr">
+        <is>
+          <t>Total
+Capacity</t>
+        </is>
+      </c>
+      <c r="L5" s="57" t="inlineStr">
+        <is>
+          <t>Util %</t>
+        </is>
+      </c>
+      <c r="M5" s="58" t="n"/>
+      <c r="N5" s="58" t="n"/>
+      <c r="O5" s="58" t="n"/>
+      <c r="P5" s="58" t="n"/>
+      <c r="Q5" s="58" t="n"/>
+      <c r="R5" s="44" t="n"/>
+      <c r="S5" s="44" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="59" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B6" s="60" t="inlineStr">
+        <is>
+          <t>P1, P2, P3, P4</t>
+        </is>
+      </c>
+      <c r="C6" s="61" t="n"/>
+      <c r="D6" s="62" t="n"/>
+      <c r="E6" s="63" t="n"/>
+      <c r="F6" s="63" t="n"/>
+      <c r="G6" s="63" t="n"/>
+      <c r="H6" s="63" t="n"/>
+      <c r="I6" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="64" t="n">
+        <v>4000</v>
+      </c>
+      <c r="K6" s="64" t="n">
+        <v>1530316</v>
+      </c>
+      <c r="L6" s="65" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M6" s="63" t="n"/>
+      <c r="N6" s="63" t="n"/>
+      <c r="O6" s="63" t="n"/>
+      <c r="P6" s="66" t="n"/>
+      <c r="Q6" s="67" t="n"/>
+      <c r="R6" s="44" t="n"/>
+      <c r="S6" s="44" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="59" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B7" s="60" t="inlineStr">
+        <is>
+          <t>P1, P2, P3, P4</t>
+        </is>
+      </c>
+      <c r="C7" s="61" t="n"/>
+      <c r="D7" s="62" t="n"/>
+      <c r="E7" s="63" t="n"/>
+      <c r="F7" s="63" t="n"/>
+      <c r="G7" s="63" t="n"/>
+      <c r="H7" s="63" t="n"/>
+      <c r="I7" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="64" t="n">
+        <v>248486</v>
+      </c>
+      <c r="K7" s="64" t="n">
+        <v>1530316</v>
+      </c>
+      <c r="L7" s="65" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="M7" s="63" t="n"/>
+      <c r="N7" s="63" t="n"/>
+      <c r="O7" s="63" t="n"/>
+      <c r="P7" s="66" t="n"/>
+      <c r="Q7" s="67" t="n"/>
+      <c r="R7" s="44" t="n"/>
+      <c r="S7" s="44" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="59" t="n">
+        <v>2031</v>
+      </c>
+      <c r="B8" s="60" t="inlineStr">
+        <is>
+          <t>P1, P2, P3</t>
+        </is>
+      </c>
+      <c r="C8" s="60" t="inlineStr">
+        <is>
+          <t>P2, P4</t>
+        </is>
+      </c>
+      <c r="D8" s="62" t="n"/>
+      <c r="E8" s="63" t="n"/>
+      <c r="F8" s="63" t="n"/>
+      <c r="G8" s="63" t="n"/>
+      <c r="H8" s="63" t="n"/>
+      <c r="I8" s="64" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="64" t="n">
+        <v>2607918</v>
+      </c>
+      <c r="K8" s="64" t="n">
+        <v>3060633</v>
+      </c>
+      <c r="L8" s="65" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="M8" s="63" t="n"/>
+      <c r="N8" s="63" t="n"/>
+      <c r="O8" s="63" t="n"/>
+      <c r="P8" s="66" t="n"/>
+      <c r="Q8" s="67" t="n"/>
+      <c r="R8" s="44" t="n"/>
+      <c r="S8" s="44" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="59" t="n">
+        <v>2032</v>
+      </c>
+      <c r="B9" s="60" t="inlineStr">
+        <is>
+          <t>P1, P2, P3</t>
+        </is>
+      </c>
+      <c r="C9" s="60" t="inlineStr">
+        <is>
+          <t>P2, P4</t>
+        </is>
+      </c>
+      <c r="D9" s="62" t="n"/>
+      <c r="E9" s="63" t="n"/>
+      <c r="F9" s="63" t="n"/>
+      <c r="G9" s="63" t="n"/>
+      <c r="H9" s="68" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I9" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" s="64" t="n">
+        <v>3708339</v>
+      </c>
+      <c r="K9" s="64" t="n">
+        <v>4646937</v>
+      </c>
+      <c r="L9" s="65" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="M9" s="63" t="n"/>
+      <c r="N9" s="63" t="n"/>
+      <c r="O9" s="63" t="n"/>
+      <c r="P9" s="66" t="n"/>
+      <c r="Q9" s="67" t="n"/>
+      <c r="R9" s="44" t="n"/>
+      <c r="S9" s="44" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="59" t="n">
+        <v>2033</v>
+      </c>
+      <c r="B10" s="60" t="inlineStr">
+        <is>
+          <t>P2, P4</t>
+        </is>
+      </c>
+      <c r="C10" s="69" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D10" s="62" t="n"/>
+      <c r="E10" s="63" t="n"/>
+      <c r="F10" s="63" t="n"/>
+      <c r="G10" s="70" t="inlineStr">
+        <is>
+          <t>P1, P3</t>
+        </is>
+      </c>
+      <c r="H10" s="68" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I10" s="64" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" s="64" t="n">
+        <v>4852239</v>
+      </c>
+      <c r="K10" s="64" t="n">
+        <v>6233241</v>
+      </c>
+      <c r="L10" s="65" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="M10" s="63" t="n"/>
+      <c r="N10" s="63" t="n"/>
+      <c r="O10" s="63" t="n"/>
+      <c r="P10" s="66" t="n"/>
+      <c r="Q10" s="67" t="n"/>
+      <c r="R10" s="44" t="n"/>
+      <c r="S10" s="44" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="59" t="n">
+        <v>2034</v>
+      </c>
+      <c r="B11" s="60" t="inlineStr">
+        <is>
+          <t>P3, P4</t>
+        </is>
+      </c>
+      <c r="C11" s="60" t="inlineStr">
+        <is>
+          <t>P2, P4</t>
+        </is>
+      </c>
+      <c r="D11" s="62" t="n"/>
+      <c r="E11" s="68" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F11" s="63" t="n"/>
+      <c r="G11" s="68" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="H11" s="68" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="I11" s="64" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" s="64" t="n">
+        <v>7011858</v>
+      </c>
+      <c r="K11" s="64" t="n">
+        <v>7819545</v>
+      </c>
+      <c r="L11" s="65" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="M11" s="63" t="n"/>
+      <c r="N11" s="63" t="n"/>
+      <c r="O11" s="63" t="n"/>
+      <c r="P11" s="66" t="n"/>
+      <c r="Q11" s="67" t="n"/>
+      <c r="R11" s="44" t="n"/>
+      <c r="S11" s="44" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="59" t="n">
+        <v>2035</v>
+      </c>
+      <c r="B12" s="69" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C12" s="60" t="inlineStr">
+        <is>
+          <t>P2, P4</t>
+        </is>
+      </c>
+      <c r="D12" s="69" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E12" s="68" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F12" s="68" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="G12" s="68" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H12" s="68" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I12" s="64" t="n">
+        <v>7</v>
+      </c>
+      <c r="J12" s="64" t="n">
+        <v>9370879</v>
+      </c>
+      <c r="K12" s="64" t="n">
+        <v>11048140</v>
+      </c>
+      <c r="L12" s="65" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="M12" s="63" t="n"/>
+      <c r="N12" s="63" t="n"/>
+      <c r="O12" s="63" t="n"/>
+      <c r="P12" s="66" t="n"/>
+      <c r="Q12" s="67" t="n"/>
+      <c r="R12" s="44" t="n"/>
+      <c r="S12" s="44" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="59" t="n">
+        <v>2036</v>
+      </c>
+      <c r="B13" s="69" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C13" s="69" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="J5" s="12" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="K5" s="12" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="L5" s="12" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="M5" s="12" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="N5" s="12" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="O5" s="12" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="P5" s="12" t="inlineStr">
-        <is>
-          <t>Util %</t>
-        </is>
-      </c>
-      <c r="Q5" s="12" t="inlineStr">
-        <is>
-          <t>OEE %</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="32" t="n">
-        <v>2029</v>
-      </c>
-      <c r="B6" s="33" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="C6" s="33" t="n">
-        <v>2029</v>
-      </c>
-      <c r="D6" s="34" t="inlineStr">
-        <is>
-          <t>P1+P2+P3+P4</t>
-        </is>
-      </c>
-      <c r="E6" s="35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F6" s="35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G6" s="35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H6" s="35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I6" s="35" t="n"/>
-      <c r="J6" s="35" t="n"/>
-      <c r="K6" s="35" t="n"/>
-      <c r="L6" s="35" t="n"/>
-      <c r="M6" s="35" t="n"/>
-      <c r="N6" s="35" t="n"/>
-      <c r="O6" s="35" t="n">
-        <v>4000</v>
-      </c>
-      <c r="P6" s="36" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q6" s="37" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="38" t="n">
-        <v>2030</v>
-      </c>
-      <c r="B7" s="39" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="C7" s="39" t="n">
-        <v>2029</v>
-      </c>
-      <c r="D7" s="40" t="inlineStr">
-        <is>
-          <t>P1+P2+P3+P4</t>
-        </is>
-      </c>
-      <c r="E7" s="41" t="n">
-        <v>35498</v>
-      </c>
-      <c r="F7" s="41" t="n">
-        <v>141992</v>
-      </c>
-      <c r="G7" s="41" t="n">
-        <v>35498</v>
-      </c>
-      <c r="H7" s="41" t="n">
-        <v>35498</v>
-      </c>
-      <c r="I7" s="41" t="n"/>
-      <c r="J7" s="41" t="n"/>
-      <c r="K7" s="41" t="n"/>
-      <c r="L7" s="41" t="n"/>
-      <c r="M7" s="41" t="n"/>
-      <c r="N7" s="41" t="n"/>
-      <c r="O7" s="41" t="n">
-        <v>248486</v>
-      </c>
-      <c r="P7" s="42" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="Q7" s="43" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="32" t="n">
-        <v>2031</v>
-      </c>
-      <c r="B8" s="33" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="C8" s="33" t="n">
-        <v>2029</v>
-      </c>
-      <c r="D8" s="34" t="inlineStr">
-        <is>
-          <t>P1+P2+P3</t>
-        </is>
-      </c>
-      <c r="E8" s="35" t="n">
-        <v>372560</v>
-      </c>
-      <c r="F8" s="35" t="n">
-        <v>332481</v>
-      </c>
-      <c r="G8" s="35" t="n">
-        <v>372560</v>
-      </c>
-      <c r="H8" s="35" t="n"/>
-      <c r="I8" s="35" t="n"/>
-      <c r="J8" s="35" t="n"/>
-      <c r="K8" s="35" t="n"/>
-      <c r="L8" s="35" t="n"/>
-      <c r="M8" s="35" t="n"/>
-      <c r="N8" s="35" t="n"/>
-      <c r="O8" s="35" t="n">
-        <v>1077601</v>
-      </c>
-      <c r="P8" s="36" t="n">
-        <v>57.7</v>
-      </c>
-      <c r="Q8" s="37" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="38" t="n">
-        <v>2031</v>
-      </c>
-      <c r="B9" s="39" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="C9" s="39" t="n">
-        <v>2031</v>
-      </c>
-      <c r="D9" s="40" t="inlineStr">
-        <is>
-          <t>P2+P4</t>
-        </is>
-      </c>
-      <c r="E9" s="41" t="n"/>
-      <c r="F9" s="41" t="n">
-        <v>1157757</v>
-      </c>
-      <c r="G9" s="41" t="n"/>
-      <c r="H9" s="41" t="n">
-        <v>372560</v>
-      </c>
-      <c r="I9" s="41" t="n"/>
-      <c r="J9" s="41" t="n"/>
-      <c r="K9" s="41" t="n"/>
-      <c r="L9" s="41" t="n"/>
-      <c r="M9" s="41" t="n"/>
-      <c r="N9" s="41" t="n"/>
-      <c r="O9" s="41" t="n">
-        <v>1530317</v>
-      </c>
-      <c r="P9" s="42" t="n">
-        <v>82</v>
-      </c>
-      <c r="Q9" s="43" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="32" t="n">
-        <v>2032</v>
-      </c>
-      <c r="B10" s="33" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="C10" s="33" t="n">
-        <v>2029</v>
-      </c>
-      <c r="D10" s="34" t="inlineStr">
-        <is>
-          <t>P1+P2+P3</t>
-        </is>
-      </c>
-      <c r="E10" s="35" t="n">
-        <v>529763</v>
-      </c>
-      <c r="F10" s="35" t="n">
-        <v>470791</v>
-      </c>
-      <c r="G10" s="35" t="n">
-        <v>529763</v>
-      </c>
-      <c r="H10" s="35" t="n"/>
-      <c r="I10" s="35" t="n"/>
-      <c r="J10" s="35" t="n"/>
-      <c r="K10" s="35" t="n"/>
-      <c r="L10" s="35" t="n"/>
-      <c r="M10" s="35" t="n"/>
-      <c r="N10" s="35" t="n"/>
-      <c r="O10" s="35" t="n">
-        <v>1530317</v>
-      </c>
-      <c r="P10" s="36" t="n">
-        <v>82</v>
-      </c>
-      <c r="Q10" s="37" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="38" t="n">
-        <v>2032</v>
-      </c>
-      <c r="B11" s="39" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="C11" s="39" t="n">
-        <v>2031</v>
-      </c>
-      <c r="D11" s="40" t="inlineStr">
-        <is>
-          <t>P2+P4</t>
-        </is>
-      </c>
-      <c r="E11" s="41" t="n"/>
-      <c r="F11" s="41" t="n">
-        <v>1000554</v>
-      </c>
-      <c r="G11" s="41" t="n"/>
-      <c r="H11" s="41" t="n">
-        <v>529763</v>
-      </c>
-      <c r="I11" s="41" t="n"/>
-      <c r="J11" s="41" t="n"/>
-      <c r="K11" s="41" t="n"/>
-      <c r="L11" s="41" t="n"/>
-      <c r="M11" s="41" t="n"/>
-      <c r="N11" s="41" t="n"/>
-      <c r="O11" s="41" t="n">
-        <v>1530317</v>
-      </c>
-      <c r="P11" s="42" t="n">
-        <v>82</v>
-      </c>
-      <c r="Q11" s="43" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="32" t="n">
-        <v>2032</v>
-      </c>
-      <c r="B12" s="33" t="inlineStr">
-        <is>
-          <t>L14</t>
-        </is>
-      </c>
-      <c r="C12" s="33" t="n">
-        <v>2032</v>
-      </c>
-      <c r="D12" s="34" t="inlineStr">
+      <c r="D13" s="69" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E12" s="35" t="n"/>
-      <c r="F12" s="35" t="n">
-        <v>647705</v>
-      </c>
-      <c r="G12" s="35" t="n"/>
-      <c r="H12" s="35" t="n"/>
-      <c r="I12" s="35" t="n"/>
-      <c r="J12" s="35" t="n"/>
-      <c r="K12" s="35" t="n"/>
-      <c r="L12" s="35" t="n"/>
-      <c r="M12" s="35" t="n"/>
-      <c r="N12" s="35" t="n"/>
-      <c r="O12" s="35" t="n">
-        <v>647705</v>
-      </c>
-      <c r="P12" s="36" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="Q12" s="37" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="38" t="n">
-        <v>2033</v>
-      </c>
-      <c r="B13" s="39" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="C13" s="39" t="n">
-        <v>2029</v>
-      </c>
-      <c r="D13" s="40" t="inlineStr">
-        <is>
-          <t>P2+P4</t>
-        </is>
-      </c>
-      <c r="E13" s="41" t="n"/>
-      <c r="F13" s="41" t="n">
-        <v>837140</v>
-      </c>
-      <c r="G13" s="41" t="n"/>
-      <c r="H13" s="41" t="n">
-        <v>693177</v>
-      </c>
-      <c r="I13" s="41" t="n"/>
-      <c r="J13" s="41" t="n"/>
-      <c r="K13" s="41" t="n"/>
-      <c r="L13" s="41" t="n"/>
-      <c r="M13" s="41" t="n"/>
-      <c r="N13" s="41" t="n"/>
-      <c r="O13" s="41" t="n">
-        <v>1530317</v>
-      </c>
-      <c r="P13" s="42" t="n">
-        <v>82</v>
-      </c>
-      <c r="Q13" s="43" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="32" t="n">
-        <v>2033</v>
-      </c>
-      <c r="B14" s="33" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="C14" s="33" t="n">
-        <v>2031</v>
-      </c>
-      <c r="D14" s="34" t="inlineStr">
+      <c r="E13" s="68" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E14" s="35" t="n"/>
-      <c r="F14" s="35" t="n">
-        <v>1586304</v>
-      </c>
-      <c r="G14" s="35" t="n"/>
-      <c r="H14" s="35" t="n"/>
-      <c r="I14" s="35" t="n"/>
-      <c r="J14" s="35" t="n"/>
-      <c r="K14" s="35" t="n"/>
-      <c r="L14" s="35" t="n"/>
-      <c r="M14" s="35" t="n"/>
-      <c r="N14" s="35" t="n"/>
-      <c r="O14" s="35" t="n">
-        <v>1586304</v>
-      </c>
-      <c r="P14" s="36" t="n">
-        <v>85</v>
-      </c>
-      <c r="Q14" s="37" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="38" t="n">
-        <v>2033</v>
-      </c>
-      <c r="B15" s="39" t="inlineStr">
-        <is>
-          <t>L7</t>
-        </is>
-      </c>
-      <c r="C15" s="39" t="n">
-        <v>2033</v>
-      </c>
-      <c r="D15" s="40" t="inlineStr">
-        <is>
-          <t>P1+P3</t>
-        </is>
-      </c>
-      <c r="E15" s="41" t="n">
-        <v>693177</v>
-      </c>
-      <c r="F15" s="41" t="n"/>
-      <c r="G15" s="41" t="n">
-        <v>693177</v>
-      </c>
-      <c r="H15" s="41" t="n"/>
-      <c r="I15" s="41" t="n"/>
-      <c r="J15" s="41" t="n"/>
-      <c r="K15" s="41" t="n"/>
-      <c r="L15" s="41" t="n"/>
-      <c r="M15" s="41" t="n"/>
-      <c r="N15" s="41" t="n"/>
-      <c r="O15" s="41" t="n">
-        <v>1386354</v>
-      </c>
-      <c r="P15" s="42" t="n">
-        <v>74.3</v>
-      </c>
-      <c r="Q15" s="43" t="n">
-        <v>82</v>
-      </c>
+      <c r="F13" s="68" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="G13" s="68" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H13" s="68" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I13" s="64" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" s="64" t="n">
+        <v>9277824</v>
+      </c>
+      <c r="K13" s="64" t="n">
+        <v>11104128</v>
+      </c>
+      <c r="L13" s="65" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="M13" s="63" t="n"/>
+      <c r="N13" s="63" t="n"/>
+      <c r="O13" s="63" t="n"/>
+      <c r="P13" s="66" t="n"/>
+      <c r="Q13" s="67" t="n"/>
+      <c r="R13" s="44" t="n"/>
+      <c r="S13" s="44" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="59" t="n">
+        <v>2037</v>
+      </c>
+      <c r="B14" s="69" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C14" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="69" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E14" s="68" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F14" s="68" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="G14" s="68" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H14" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="64" t="n">
+        <v>7</v>
+      </c>
+      <c r="J14" s="64" t="n">
+        <v>4271659</v>
+      </c>
+      <c r="K14" s="64" t="n">
+        <v>11104128</v>
+      </c>
+      <c r="L14" s="65" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="M14" s="63" t="n"/>
+      <c r="N14" s="63" t="n"/>
+      <c r="O14" s="63" t="n"/>
+      <c r="P14" s="66" t="n"/>
+      <c r="Q14" s="67" t="n"/>
+      <c r="R14" s="44" t="n"/>
+      <c r="S14" s="44" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="59" t="n">
+        <v>2038</v>
+      </c>
+      <c r="B15" s="69" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C15" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="69" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E15" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="68" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="G15" s="68" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H15" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" s="64" t="n">
+        <v>7</v>
+      </c>
+      <c r="J15" s="64" t="n">
+        <v>1216264</v>
+      </c>
+      <c r="K15" s="64" t="n">
+        <v>11104128</v>
+      </c>
+      <c r="L15" s="65" t="n">
+        <v>11</v>
+      </c>
+      <c r="M15" s="63" t="n"/>
+      <c r="N15" s="63" t="n"/>
+      <c r="O15" s="63" t="n"/>
+      <c r="P15" s="66" t="n"/>
+      <c r="Q15" s="67" t="n"/>
+      <c r="R15" s="44" t="n"/>
+      <c r="S15" s="44" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="32" t="n">
-        <v>2033</v>
-      </c>
-      <c r="B16" s="33" t="inlineStr">
-        <is>
-          <t>L14</t>
-        </is>
-      </c>
-      <c r="C16" s="33" t="n">
-        <v>2032</v>
-      </c>
-      <c r="D16" s="34" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E16" s="35" t="n"/>
-      <c r="F16" s="35" t="n">
-        <v>349264</v>
-      </c>
-      <c r="G16" s="35" t="n"/>
-      <c r="H16" s="35" t="n"/>
-      <c r="I16" s="35" t="n"/>
-      <c r="J16" s="35" t="n"/>
-      <c r="K16" s="35" t="n"/>
-      <c r="L16" s="35" t="n"/>
-      <c r="M16" s="35" t="n"/>
-      <c r="N16" s="35" t="n"/>
-      <c r="O16" s="35" t="n">
-        <v>349264</v>
-      </c>
-      <c r="P16" s="36" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="Q16" s="37" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="38" t="n">
-        <v>2034</v>
-      </c>
-      <c r="B17" s="39" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="C17" s="39" t="n">
-        <v>2029</v>
-      </c>
-      <c r="D17" s="40" t="inlineStr">
-        <is>
-          <t>P3+P4</t>
-        </is>
-      </c>
-      <c r="E17" s="41" t="n"/>
-      <c r="F17" s="41" t="n"/>
-      <c r="G17" s="41" t="n">
-        <v>1001694</v>
-      </c>
-      <c r="H17" s="41" t="n">
-        <v>528623</v>
-      </c>
-      <c r="I17" s="41" t="n"/>
-      <c r="J17" s="41" t="n"/>
-      <c r="K17" s="41" t="n"/>
-      <c r="L17" s="41" t="n"/>
-      <c r="M17" s="41" t="n"/>
-      <c r="N17" s="41" t="n"/>
-      <c r="O17" s="41" t="n">
-        <v>1530317</v>
-      </c>
-      <c r="P17" s="42" t="n">
-        <v>82</v>
-      </c>
-      <c r="Q17" s="43" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="32" t="n">
-        <v>2034</v>
-      </c>
-      <c r="B18" s="33" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="C18" s="33" t="n">
-        <v>2031</v>
-      </c>
-      <c r="D18" s="34" t="inlineStr">
-        <is>
-          <t>P2+P4</t>
-        </is>
-      </c>
-      <c r="E18" s="35" t="n"/>
-      <c r="F18" s="35" t="n">
-        <v>1057246</v>
-      </c>
-      <c r="G18" s="35" t="n"/>
-      <c r="H18" s="35" t="n">
-        <v>473071</v>
-      </c>
-      <c r="I18" s="35" t="n"/>
-      <c r="J18" s="35" t="n"/>
-      <c r="K18" s="35" t="n"/>
-      <c r="L18" s="35" t="n"/>
-      <c r="M18" s="35" t="n"/>
-      <c r="N18" s="35" t="n"/>
-      <c r="O18" s="35" t="n">
-        <v>1530317</v>
-      </c>
-      <c r="P18" s="36" t="n">
-        <v>82</v>
-      </c>
-      <c r="Q18" s="37" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="38" t="n">
-        <v>2034</v>
-      </c>
-      <c r="B19" s="39" t="inlineStr">
-        <is>
-          <t>L5</t>
-        </is>
-      </c>
-      <c r="C19" s="39" t="n">
-        <v>2034</v>
-      </c>
-      <c r="D19" s="40" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E19" s="41" t="n"/>
-      <c r="F19" s="41" t="n">
-        <v>1419214</v>
-      </c>
-      <c r="G19" s="41" t="n"/>
-      <c r="H19" s="41" t="n"/>
-      <c r="I19" s="41" t="n"/>
-      <c r="J19" s="41" t="n"/>
-      <c r="K19" s="41" t="n"/>
-      <c r="L19" s="41" t="n"/>
-      <c r="M19" s="41" t="n"/>
-      <c r="N19" s="41" t="n"/>
-      <c r="O19" s="41" t="n">
-        <v>1419214</v>
-      </c>
-      <c r="P19" s="42" t="n">
-        <v>76</v>
-      </c>
-      <c r="Q19" s="43" t="n">
-        <v>85</v>
-      </c>
+      <c r="A16" s="73" t="n"/>
+      <c r="B16" s="61" t="n"/>
+      <c r="C16" s="61" t="n"/>
+      <c r="D16" s="62" t="n"/>
+      <c r="E16" s="63" t="n"/>
+      <c r="F16" s="63" t="n"/>
+      <c r="G16" s="63" t="n"/>
+      <c r="H16" s="63" t="n"/>
+      <c r="I16" s="63" t="n"/>
+      <c r="J16" s="63" t="n"/>
+      <c r="K16" s="63" t="n"/>
+      <c r="L16" s="63" t="n"/>
+      <c r="M16" s="63" t="n"/>
+      <c r="N16" s="63" t="n"/>
+      <c r="O16" s="63" t="n"/>
+      <c r="P16" s="66" t="n"/>
+      <c r="Q16" s="67" t="n"/>
+      <c r="R16" s="44" t="n"/>
+      <c r="S16" s="44" t="n"/>
+    </row>
+    <row r="17" ht="14" customHeight="1">
+      <c r="A17" s="73" t="n"/>
+      <c r="B17" s="33" t="inlineStr"/>
+      <c r="C17" s="74" t="inlineStr">
+        <is>
+          <t>Single-product line (no changeover)</t>
+        </is>
+      </c>
+      <c r="D17" s="62" t="n"/>
+      <c r="E17" s="63" t="n"/>
+      <c r="F17" s="63" t="n"/>
+      <c r="G17" s="63" t="n"/>
+      <c r="H17" s="63" t="n"/>
+      <c r="I17" s="63" t="n"/>
+      <c r="J17" s="63" t="n"/>
+      <c r="K17" s="63" t="n"/>
+      <c r="L17" s="63" t="n"/>
+      <c r="M17" s="63" t="n"/>
+      <c r="N17" s="63" t="n"/>
+      <c r="O17" s="63" t="n"/>
+      <c r="P17" s="66" t="n"/>
+      <c r="Q17" s="67" t="n"/>
+      <c r="R17" s="44" t="n"/>
+      <c r="S17" s="44" t="n"/>
+    </row>
+    <row r="18" ht="14" customHeight="1">
+      <c r="A18" s="73" t="n"/>
+      <c r="B18" s="75" t="inlineStr"/>
+      <c r="C18" s="74" t="inlineStr">
+        <is>
+          <t>Multi-product line (changeover penalty applies)</t>
+        </is>
+      </c>
+      <c r="D18" s="62" t="n"/>
+      <c r="E18" s="63" t="n"/>
+      <c r="F18" s="63" t="n"/>
+      <c r="G18" s="63" t="n"/>
+      <c r="H18" s="63" t="n"/>
+      <c r="I18" s="63" t="n"/>
+      <c r="J18" s="63" t="n"/>
+      <c r="K18" s="63" t="n"/>
+      <c r="L18" s="63" t="n"/>
+      <c r="M18" s="63" t="n"/>
+      <c r="N18" s="63" t="n"/>
+      <c r="O18" s="63" t="n"/>
+      <c r="P18" s="66" t="n"/>
+      <c r="Q18" s="67" t="n"/>
+      <c r="R18" s="44" t="n"/>
+      <c r="S18" s="44" t="n"/>
+    </row>
+    <row r="19" ht="14" customHeight="1">
+      <c r="A19" s="73" t="n"/>
+      <c r="B19" s="76" t="inlineStr"/>
+      <c r="C19" s="74" t="inlineStr">
+        <is>
+          <t>Line open but idle this year</t>
+        </is>
+      </c>
+      <c r="D19" s="62" t="n"/>
+      <c r="E19" s="63" t="n"/>
+      <c r="F19" s="63" t="n"/>
+      <c r="G19" s="63" t="n"/>
+      <c r="H19" s="63" t="n"/>
+      <c r="I19" s="63" t="n"/>
+      <c r="J19" s="63" t="n"/>
+      <c r="K19" s="63" t="n"/>
+      <c r="L19" s="63" t="n"/>
+      <c r="M19" s="63" t="n"/>
+      <c r="N19" s="63" t="n"/>
+      <c r="O19" s="63" t="n"/>
+      <c r="P19" s="66" t="n"/>
+      <c r="Q19" s="67" t="n"/>
+      <c r="R19" s="44" t="n"/>
+      <c r="S19" s="44" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="32" t="n">
-        <v>2034</v>
-      </c>
-      <c r="B20" s="33" t="inlineStr">
-        <is>
-          <t>L7</t>
-        </is>
-      </c>
-      <c r="C20" s="33" t="n">
-        <v>2033</v>
-      </c>
-      <c r="D20" s="34" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E20" s="35" t="n">
-        <v>1001694</v>
-      </c>
-      <c r="F20" s="35" t="n"/>
-      <c r="G20" s="35" t="n"/>
-      <c r="H20" s="35" t="n"/>
-      <c r="I20" s="35" t="n"/>
-      <c r="J20" s="35" t="n"/>
-      <c r="K20" s="35" t="n"/>
-      <c r="L20" s="35" t="n"/>
-      <c r="M20" s="35" t="n"/>
-      <c r="N20" s="35" t="n"/>
-      <c r="O20" s="35" t="n">
-        <v>1001694</v>
-      </c>
-      <c r="P20" s="36" t="n">
-        <v>53.7</v>
-      </c>
-      <c r="Q20" s="37" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="38" t="n">
-        <v>2034</v>
-      </c>
-      <c r="B21" s="39" t="inlineStr">
-        <is>
-          <t>L14</t>
-        </is>
-      </c>
-      <c r="C21" s="39" t="n">
-        <v>2032</v>
-      </c>
-      <c r="D21" s="40" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E21" s="41" t="n"/>
-      <c r="F21" s="41" t="n">
-        <v>1530317</v>
-      </c>
-      <c r="G21" s="41" t="n"/>
-      <c r="H21" s="41" t="n"/>
-      <c r="I21" s="41" t="n"/>
-      <c r="J21" s="41" t="n"/>
-      <c r="K21" s="41" t="n"/>
-      <c r="L21" s="41" t="n"/>
-      <c r="M21" s="41" t="n"/>
-      <c r="N21" s="41" t="n"/>
-      <c r="O21" s="41" t="n">
-        <v>1530317</v>
-      </c>
-      <c r="P21" s="42" t="n">
-        <v>82</v>
-      </c>
-      <c r="Q21" s="43" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="32" t="n">
-        <v>2035</v>
-      </c>
-      <c r="B22" s="33" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="C22" s="33" t="n">
-        <v>2029</v>
-      </c>
-      <c r="D22" s="34" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E22" s="35" t="n"/>
-      <c r="F22" s="35" t="n">
-        <v>1586304</v>
-      </c>
-      <c r="G22" s="35" t="n"/>
-      <c r="H22" s="35" t="n"/>
-      <c r="I22" s="35" t="n"/>
-      <c r="J22" s="35" t="n"/>
-      <c r="K22" s="35" t="n"/>
-      <c r="L22" s="35" t="n"/>
-      <c r="M22" s="35" t="n"/>
-      <c r="N22" s="35" t="n"/>
-      <c r="O22" s="35" t="n">
-        <v>1586304</v>
-      </c>
-      <c r="P22" s="36" t="n">
-        <v>85</v>
-      </c>
-      <c r="Q22" s="37" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="38" t="n">
-        <v>2035</v>
-      </c>
-      <c r="B23" s="39" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="C23" s="39" t="n">
-        <v>2031</v>
-      </c>
-      <c r="D23" s="40" t="inlineStr">
-        <is>
-          <t>P2+P4</t>
-        </is>
-      </c>
-      <c r="E23" s="41" t="n"/>
-      <c r="F23" s="41" t="n">
-        <v>191620</v>
-      </c>
-      <c r="G23" s="41" t="n"/>
-      <c r="H23" s="41" t="n">
-        <v>1338697</v>
-      </c>
-      <c r="I23" s="41" t="n"/>
-      <c r="J23" s="41" t="n"/>
-      <c r="K23" s="41" t="n"/>
-      <c r="L23" s="41" t="n"/>
-      <c r="M23" s="41" t="n"/>
-      <c r="N23" s="41" t="n"/>
-      <c r="O23" s="41" t="n">
-        <v>1530317</v>
-      </c>
-      <c r="P23" s="42" t="n">
-        <v>82</v>
-      </c>
-      <c r="Q23" s="43" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="32" t="n">
-        <v>2035</v>
-      </c>
-      <c r="B24" s="33" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="C24" s="33" t="n">
-        <v>2035</v>
-      </c>
-      <c r="D24" s="34" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E24" s="35" t="n"/>
-      <c r="F24" s="35" t="n">
-        <v>559872</v>
-      </c>
-      <c r="G24" s="35" t="n"/>
-      <c r="H24" s="35" t="n"/>
-      <c r="I24" s="35" t="n"/>
-      <c r="J24" s="35" t="n"/>
-      <c r="K24" s="35" t="n"/>
-      <c r="L24" s="35" t="n"/>
-      <c r="M24" s="35" t="n"/>
-      <c r="N24" s="35" t="n"/>
-      <c r="O24" s="35" t="n">
-        <v>559872</v>
-      </c>
-      <c r="P24" s="36" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q24" s="37" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="38" t="n">
-        <v>2035</v>
-      </c>
-      <c r="B25" s="39" t="inlineStr">
-        <is>
-          <t>L5</t>
-        </is>
-      </c>
-      <c r="C25" s="39" t="n">
-        <v>2034</v>
-      </c>
-      <c r="D25" s="40" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E25" s="41" t="n"/>
-      <c r="F25" s="41" t="n">
-        <v>1586304</v>
-      </c>
-      <c r="G25" s="41" t="n"/>
-      <c r="H25" s="41" t="n"/>
-      <c r="I25" s="41" t="n"/>
-      <c r="J25" s="41" t="n"/>
-      <c r="K25" s="41" t="n"/>
-      <c r="L25" s="41" t="n"/>
-      <c r="M25" s="41" t="n"/>
-      <c r="N25" s="41" t="n"/>
-      <c r="O25" s="41" t="n">
-        <v>1586304</v>
-      </c>
-      <c r="P25" s="42" t="n">
-        <v>85</v>
-      </c>
-      <c r="Q25" s="43" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="32" t="n">
-        <v>2035</v>
-      </c>
-      <c r="B26" s="33" t="inlineStr">
-        <is>
-          <t>L6</t>
-        </is>
-      </c>
-      <c r="C26" s="33" t="n">
-        <v>2035</v>
-      </c>
-      <c r="D26" s="34" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="E26" s="35" t="n"/>
-      <c r="F26" s="35" t="n"/>
-      <c r="G26" s="35" t="n">
-        <v>1338697</v>
-      </c>
-      <c r="H26" s="35" t="n"/>
-      <c r="I26" s="35" t="n"/>
-      <c r="J26" s="35" t="n"/>
-      <c r="K26" s="35" t="n"/>
-      <c r="L26" s="35" t="n"/>
-      <c r="M26" s="35" t="n"/>
-      <c r="N26" s="35" t="n"/>
-      <c r="O26" s="35" t="n">
-        <v>1338697</v>
-      </c>
-      <c r="P26" s="36" t="n">
-        <v>71.7</v>
-      </c>
-      <c r="Q26" s="37" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="38" t="n">
-        <v>2035</v>
-      </c>
-      <c r="B27" s="39" t="inlineStr">
-        <is>
-          <t>L7</t>
-        </is>
-      </c>
-      <c r="C27" s="39" t="n">
-        <v>2033</v>
-      </c>
-      <c r="D27" s="40" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E27" s="41" t="n">
-        <v>1338697</v>
-      </c>
-      <c r="F27" s="41" t="n"/>
-      <c r="G27" s="41" t="n"/>
-      <c r="H27" s="41" t="n"/>
-      <c r="I27" s="41" t="n"/>
-      <c r="J27" s="41" t="n"/>
-      <c r="K27" s="41" t="n"/>
-      <c r="L27" s="41" t="n"/>
-      <c r="M27" s="41" t="n"/>
-      <c r="N27" s="41" t="n"/>
-      <c r="O27" s="41" t="n">
-        <v>1338697</v>
-      </c>
-      <c r="P27" s="42" t="n">
-        <v>71.7</v>
-      </c>
-      <c r="Q27" s="43" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="32" t="n">
-        <v>2035</v>
-      </c>
-      <c r="B28" s="33" t="inlineStr">
-        <is>
-          <t>L14</t>
-        </is>
-      </c>
-      <c r="C28" s="33" t="n">
-        <v>2032</v>
-      </c>
-      <c r="D28" s="34" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E28" s="35" t="n"/>
-      <c r="F28" s="35" t="n">
-        <v>1430688</v>
-      </c>
-      <c r="G28" s="35" t="n"/>
-      <c r="H28" s="35" t="n"/>
-      <c r="I28" s="35" t="n"/>
-      <c r="J28" s="35" t="n"/>
-      <c r="K28" s="35" t="n"/>
-      <c r="L28" s="35" t="n"/>
-      <c r="M28" s="35" t="n"/>
-      <c r="N28" s="35" t="n"/>
-      <c r="O28" s="35" t="n">
-        <v>1430688</v>
-      </c>
-      <c r="P28" s="36" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="Q28" s="37" t="n">
-        <v>85</v>
-      </c>
+      <c r="A20" s="73" t="n"/>
+      <c r="B20" s="61" t="n"/>
+      <c r="C20" s="61" t="n"/>
+      <c r="D20" s="62" t="n"/>
+      <c r="E20" s="63" t="n"/>
+      <c r="F20" s="63" t="n"/>
+      <c r="G20" s="63" t="n"/>
+      <c r="H20" s="63" t="n"/>
+      <c r="I20" s="63" t="n"/>
+      <c r="J20" s="63" t="n"/>
+      <c r="K20" s="63" t="n"/>
+      <c r="L20" s="63" t="n"/>
+      <c r="M20" s="63" t="n"/>
+      <c r="N20" s="63" t="n"/>
+      <c r="O20" s="63" t="n"/>
+      <c r="P20" s="66" t="n"/>
+      <c r="Q20" s="67" t="n"/>
+      <c r="R20" s="44" t="n"/>
+      <c r="S20" s="44" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="77" t="inlineStr">
+        <is>
+          <t>LINES USED</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="n"/>
+      <c r="C21" s="24" t="n"/>
+      <c r="D21" s="24" t="n"/>
+      <c r="E21" s="24" t="n"/>
+      <c r="F21" s="24" t="n"/>
+      <c r="G21" s="24" t="n"/>
+      <c r="H21" s="24" t="n"/>
+      <c r="I21" s="24" t="n"/>
+      <c r="J21" s="24" t="n"/>
+      <c r="K21" s="24" t="n"/>
+      <c r="L21" s="25" t="n"/>
+      <c r="M21" s="63" t="n"/>
+      <c r="N21" s="63" t="n"/>
+      <c r="O21" s="63" t="n"/>
+      <c r="P21" s="66" t="n"/>
+      <c r="Q21" s="67" t="n"/>
+      <c r="R21" s="44" t="n"/>
+      <c r="S21" s="44" t="n"/>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="78" t="inlineStr">
+        <is>
+          <t>L1  intro=2029  products=[P1, P2, P3, P4]  OEE=82%  tooling=[12 mech / 12 opt total]</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="n"/>
+      <c r="C22" s="24" t="n"/>
+      <c r="D22" s="24" t="n"/>
+      <c r="E22" s="24" t="n"/>
+      <c r="F22" s="24" t="n"/>
+      <c r="G22" s="24" t="n"/>
+      <c r="H22" s="24" t="n"/>
+      <c r="I22" s="24" t="n"/>
+      <c r="J22" s="24" t="n"/>
+      <c r="K22" s="24" t="n"/>
+      <c r="L22" s="25" t="n"/>
+      <c r="M22" s="63" t="n"/>
+      <c r="N22" s="63" t="n"/>
+      <c r="O22" s="63" t="n"/>
+      <c r="P22" s="66" t="n"/>
+      <c r="Q22" s="67" t="n"/>
+      <c r="R22" s="44" t="n"/>
+      <c r="S22" s="44" t="n"/>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="78" t="inlineStr">
+        <is>
+          <t>L2  intro=2031  products=[P2, P4]  OEE=82%  tooling=[12 mech / 12 opt total]</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="n"/>
+      <c r="C23" s="24" t="n"/>
+      <c r="D23" s="24" t="n"/>
+      <c r="E23" s="24" t="n"/>
+      <c r="F23" s="24" t="n"/>
+      <c r="G23" s="24" t="n"/>
+      <c r="H23" s="24" t="n"/>
+      <c r="I23" s="24" t="n"/>
+      <c r="J23" s="24" t="n"/>
+      <c r="K23" s="24" t="n"/>
+      <c r="L23" s="25" t="n"/>
+      <c r="M23" s="63" t="n"/>
+      <c r="N23" s="63" t="n"/>
+      <c r="O23" s="63" t="n"/>
+      <c r="P23" s="66" t="n"/>
+      <c r="Q23" s="67" t="n"/>
+      <c r="R23" s="44" t="n"/>
+      <c r="S23" s="44" t="n"/>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="78" t="inlineStr">
+        <is>
+          <t>L3  intro=2035  products=[P2]  OEE=85%  tooling=[12 mech / 12 opt total]</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="n"/>
+      <c r="C24" s="24" t="n"/>
+      <c r="D24" s="24" t="n"/>
+      <c r="E24" s="24" t="n"/>
+      <c r="F24" s="24" t="n"/>
+      <c r="G24" s="24" t="n"/>
+      <c r="H24" s="24" t="n"/>
+      <c r="I24" s="24" t="n"/>
+      <c r="J24" s="24" t="n"/>
+      <c r="K24" s="24" t="n"/>
+      <c r="L24" s="25" t="n"/>
+      <c r="M24" s="63" t="n"/>
+      <c r="N24" s="63" t="n"/>
+      <c r="O24" s="63" t="n"/>
+      <c r="P24" s="66" t="n"/>
+      <c r="Q24" s="67" t="n"/>
+      <c r="R24" s="44" t="n"/>
+      <c r="S24" s="44" t="n"/>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="78" t="inlineStr">
+        <is>
+          <t>L5  intro=2034  products=[P2]  OEE=85%  tooling=[12 mech / 12 opt total]</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="n"/>
+      <c r="C25" s="24" t="n"/>
+      <c r="D25" s="24" t="n"/>
+      <c r="E25" s="24" t="n"/>
+      <c r="F25" s="24" t="n"/>
+      <c r="G25" s="24" t="n"/>
+      <c r="H25" s="24" t="n"/>
+      <c r="I25" s="24" t="n"/>
+      <c r="J25" s="24" t="n"/>
+      <c r="K25" s="24" t="n"/>
+      <c r="L25" s="25" t="n"/>
+      <c r="M25" s="63" t="n"/>
+      <c r="N25" s="63" t="n"/>
+      <c r="O25" s="63" t="n"/>
+      <c r="P25" s="66" t="n"/>
+      <c r="Q25" s="67" t="n"/>
+      <c r="R25" s="44" t="n"/>
+      <c r="S25" s="44" t="n"/>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="78" t="inlineStr">
+        <is>
+          <t>L6  intro=2035  products=[P3]  OEE=85%  tooling=[12 mech / 12 opt total]</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="n"/>
+      <c r="C26" s="24" t="n"/>
+      <c r="D26" s="24" t="n"/>
+      <c r="E26" s="24" t="n"/>
+      <c r="F26" s="24" t="n"/>
+      <c r="G26" s="24" t="n"/>
+      <c r="H26" s="24" t="n"/>
+      <c r="I26" s="24" t="n"/>
+      <c r="J26" s="24" t="n"/>
+      <c r="K26" s="24" t="n"/>
+      <c r="L26" s="25" t="n"/>
+      <c r="M26" s="63" t="n"/>
+      <c r="N26" s="63" t="n"/>
+      <c r="O26" s="63" t="n"/>
+      <c r="P26" s="66" t="n"/>
+      <c r="Q26" s="67" t="n"/>
+      <c r="R26" s="44" t="n"/>
+      <c r="S26" s="44" t="n"/>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="78" t="inlineStr">
+        <is>
+          <t>L7  intro=2033  products=[P1, P3]  OEE=82%  tooling=[12 mech / 12 opt total]</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="n"/>
+      <c r="C27" s="24" t="n"/>
+      <c r="D27" s="24" t="n"/>
+      <c r="E27" s="24" t="n"/>
+      <c r="F27" s="24" t="n"/>
+      <c r="G27" s="24" t="n"/>
+      <c r="H27" s="24" t="n"/>
+      <c r="I27" s="24" t="n"/>
+      <c r="J27" s="24" t="n"/>
+      <c r="K27" s="24" t="n"/>
+      <c r="L27" s="25" t="n"/>
+      <c r="M27" s="63" t="n"/>
+      <c r="N27" s="63" t="n"/>
+      <c r="O27" s="63" t="n"/>
+      <c r="P27" s="66" t="n"/>
+      <c r="Q27" s="67" t="n"/>
+      <c r="R27" s="44" t="n"/>
+      <c r="S27" s="44" t="n"/>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="78" t="inlineStr">
+        <is>
+          <t>L14  intro=2032  products=[P2]  OEE=85%  tooling=[12 mech / 12 opt total]</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="n"/>
+      <c r="C28" s="24" t="n"/>
+      <c r="D28" s="24" t="n"/>
+      <c r="E28" s="24" t="n"/>
+      <c r="F28" s="24" t="n"/>
+      <c r="G28" s="24" t="n"/>
+      <c r="H28" s="24" t="n"/>
+      <c r="I28" s="24" t="n"/>
+      <c r="J28" s="24" t="n"/>
+      <c r="K28" s="24" t="n"/>
+      <c r="L28" s="25" t="n"/>
+      <c r="M28" s="63" t="n"/>
+      <c r="N28" s="63" t="n"/>
+      <c r="O28" s="63" t="n"/>
+      <c r="P28" s="66" t="n"/>
+      <c r="Q28" s="67" t="n"/>
+      <c r="R28" s="44" t="n"/>
+      <c r="S28" s="44" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="38" t="n">
-        <v>2036</v>
-      </c>
-      <c r="B29" s="39" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="C29" s="39" t="n">
-        <v>2029</v>
-      </c>
-      <c r="D29" s="40" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E29" s="41" t="n"/>
-      <c r="F29" s="41" t="n">
-        <v>1586304</v>
-      </c>
-      <c r="G29" s="41" t="n"/>
-      <c r="H29" s="41" t="n"/>
-      <c r="I29" s="41" t="n"/>
-      <c r="J29" s="41" t="n"/>
-      <c r="K29" s="41" t="n"/>
-      <c r="L29" s="41" t="n"/>
-      <c r="M29" s="41" t="n"/>
-      <c r="N29" s="41" t="n"/>
-      <c r="O29" s="41" t="n">
-        <v>1586304</v>
-      </c>
-      <c r="P29" s="42" t="n">
-        <v>85</v>
-      </c>
-      <c r="Q29" s="43" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="32" t="n">
-        <v>2036</v>
-      </c>
-      <c r="B30" s="33" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="C30" s="33" t="n">
-        <v>2031</v>
-      </c>
-      <c r="D30" s="34" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="E30" s="35" t="n"/>
-      <c r="F30" s="35" t="n"/>
-      <c r="G30" s="35" t="n"/>
-      <c r="H30" s="35" t="n">
-        <v>1286832</v>
-      </c>
-      <c r="I30" s="35" t="n"/>
-      <c r="J30" s="35" t="n"/>
-      <c r="K30" s="35" t="n"/>
-      <c r="L30" s="35" t="n"/>
-      <c r="M30" s="35" t="n"/>
-      <c r="N30" s="35" t="n"/>
-      <c r="O30" s="35" t="n">
-        <v>1286832</v>
-      </c>
-      <c r="P30" s="36" t="n">
-        <v>69</v>
-      </c>
-      <c r="Q30" s="37" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="38" t="n">
-        <v>2036</v>
-      </c>
-      <c r="B31" s="39" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="C31" s="39" t="n">
-        <v>2035</v>
-      </c>
-      <c r="D31" s="40" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E31" s="41" t="n"/>
-      <c r="F31" s="41" t="n">
-        <v>1530317</v>
-      </c>
-      <c r="G31" s="41" t="n"/>
-      <c r="H31" s="41" t="n"/>
-      <c r="I31" s="41" t="n"/>
-      <c r="J31" s="41" t="n"/>
-      <c r="K31" s="41" t="n"/>
-      <c r="L31" s="41" t="n"/>
-      <c r="M31" s="41" t="n"/>
-      <c r="N31" s="41" t="n"/>
-      <c r="O31" s="41" t="n">
-        <v>1530317</v>
-      </c>
-      <c r="P31" s="42" t="n">
-        <v>82</v>
-      </c>
-      <c r="Q31" s="43" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="32" t="n">
-        <v>2036</v>
-      </c>
-      <c r="B32" s="33" t="inlineStr">
-        <is>
-          <t>L5</t>
-        </is>
-      </c>
-      <c r="C32" s="33" t="n">
-        <v>2034</v>
-      </c>
-      <c r="D32" s="34" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E32" s="35" t="n"/>
-      <c r="F32" s="35" t="n">
-        <v>714403</v>
-      </c>
-      <c r="G32" s="35" t="n"/>
-      <c r="H32" s="35" t="n"/>
-      <c r="I32" s="35" t="n"/>
-      <c r="J32" s="35" t="n"/>
-      <c r="K32" s="35" t="n"/>
-      <c r="L32" s="35" t="n"/>
-      <c r="M32" s="35" t="n"/>
-      <c r="N32" s="35" t="n"/>
-      <c r="O32" s="35" t="n">
-        <v>714403</v>
-      </c>
-      <c r="P32" s="36" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="Q32" s="37" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="38" t="n">
-        <v>2036</v>
-      </c>
-      <c r="B33" s="39" t="inlineStr">
-        <is>
-          <t>L6</t>
-        </is>
-      </c>
-      <c r="C33" s="39" t="n">
-        <v>2035</v>
-      </c>
-      <c r="D33" s="40" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="E33" s="41" t="n"/>
-      <c r="F33" s="41" t="n"/>
-      <c r="G33" s="41" t="n">
-        <v>1286832</v>
-      </c>
-      <c r="H33" s="41" t="n"/>
-      <c r="I33" s="41" t="n"/>
-      <c r="J33" s="41" t="n"/>
-      <c r="K33" s="41" t="n"/>
-      <c r="L33" s="41" t="n"/>
-      <c r="M33" s="41" t="n"/>
-      <c r="N33" s="41" t="n"/>
-      <c r="O33" s="41" t="n">
-        <v>1286832</v>
-      </c>
-      <c r="P33" s="42" t="n">
-        <v>69</v>
-      </c>
-      <c r="Q33" s="43" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="32" t="n">
-        <v>2036</v>
-      </c>
-      <c r="B34" s="33" t="inlineStr">
-        <is>
-          <t>L7</t>
-        </is>
-      </c>
-      <c r="C34" s="33" t="n">
-        <v>2033</v>
-      </c>
-      <c r="D34" s="34" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E34" s="35" t="n">
-        <v>1286832</v>
-      </c>
-      <c r="F34" s="35" t="n"/>
-      <c r="G34" s="35" t="n"/>
-      <c r="H34" s="35" t="n"/>
-      <c r="I34" s="35" t="n"/>
-      <c r="J34" s="35" t="n"/>
-      <c r="K34" s="35" t="n"/>
-      <c r="L34" s="35" t="n"/>
-      <c r="M34" s="35" t="n"/>
-      <c r="N34" s="35" t="n"/>
-      <c r="O34" s="35" t="n">
-        <v>1286832</v>
-      </c>
-      <c r="P34" s="36" t="n">
-        <v>69</v>
-      </c>
-      <c r="Q34" s="37" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="38" t="n">
-        <v>2036</v>
-      </c>
-      <c r="B35" s="39" t="inlineStr">
-        <is>
-          <t>L14</t>
-        </is>
-      </c>
-      <c r="C35" s="39" t="n">
-        <v>2032</v>
-      </c>
-      <c r="D35" s="40" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E35" s="41" t="n"/>
-      <c r="F35" s="41" t="n">
-        <v>1586304</v>
-      </c>
-      <c r="G35" s="41" t="n"/>
-      <c r="H35" s="41" t="n"/>
-      <c r="I35" s="41" t="n"/>
-      <c r="J35" s="41" t="n"/>
-      <c r="K35" s="41" t="n"/>
-      <c r="L35" s="41" t="n"/>
-      <c r="M35" s="41" t="n"/>
-      <c r="N35" s="41" t="n"/>
-      <c r="O35" s="41" t="n">
-        <v>1586304</v>
-      </c>
-      <c r="P35" s="42" t="n">
-        <v>85</v>
-      </c>
-      <c r="Q35" s="43" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="32" t="n">
-        <v>2037</v>
-      </c>
-      <c r="B36" s="33" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="C36" s="33" t="n">
-        <v>2029</v>
-      </c>
-      <c r="D36" s="34" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="E36" s="35" t="n"/>
-      <c r="F36" s="35" t="n"/>
-      <c r="G36" s="35" t="n"/>
-      <c r="H36" s="35" t="n">
-        <v>610237</v>
-      </c>
-      <c r="I36" s="35" t="n"/>
-      <c r="J36" s="35" t="n"/>
-      <c r="K36" s="35" t="n"/>
-      <c r="L36" s="35" t="n"/>
-      <c r="M36" s="35" t="n"/>
-      <c r="N36" s="35" t="n"/>
-      <c r="O36" s="35" t="n">
-        <v>610237</v>
-      </c>
-      <c r="P36" s="36" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="Q36" s="37" t="n">
-        <v>85</v>
-      </c>
+      <c r="A29" s="73" t="n"/>
+      <c r="B29" s="61" t="n"/>
+      <c r="C29" s="61" t="n"/>
+      <c r="D29" s="62" t="n"/>
+      <c r="E29" s="63" t="n"/>
+      <c r="F29" s="63" t="n"/>
+      <c r="G29" s="63" t="n"/>
+      <c r="H29" s="63" t="n"/>
+      <c r="I29" s="63" t="n"/>
+      <c r="J29" s="63" t="n"/>
+      <c r="K29" s="63" t="n"/>
+      <c r="L29" s="63" t="n"/>
+      <c r="M29" s="63" t="n"/>
+      <c r="N29" s="63" t="n"/>
+      <c r="O29" s="63" t="n"/>
+      <c r="P29" s="66" t="n"/>
+      <c r="Q29" s="67" t="n"/>
+      <c r="R29" s="44" t="n"/>
+      <c r="S29" s="44" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="77" t="inlineStr">
+        <is>
+          <t>COST BREAKDOWN</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="n"/>
+      <c r="C30" s="24" t="n"/>
+      <c r="D30" s="24" t="n"/>
+      <c r="E30" s="24" t="n"/>
+      <c r="F30" s="24" t="n"/>
+      <c r="G30" s="24" t="n"/>
+      <c r="H30" s="24" t="n"/>
+      <c r="I30" s="24" t="n"/>
+      <c r="J30" s="24" t="n"/>
+      <c r="K30" s="24" t="n"/>
+      <c r="L30" s="25" t="n"/>
+      <c r="M30" s="63" t="n"/>
+      <c r="N30" s="63" t="n"/>
+      <c r="O30" s="63" t="n"/>
+      <c r="P30" s="66" t="n"/>
+      <c r="Q30" s="67" t="n"/>
+      <c r="R30" s="44" t="n"/>
+      <c r="S30" s="44" t="n"/>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="78" t="inlineStr">
+        <is>
+          <t>New lines: 7 × $0</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="n"/>
+      <c r="C31" s="24" t="n"/>
+      <c r="D31" s="24" t="n"/>
+      <c r="E31" s="24" t="n"/>
+      <c r="F31" s="24" t="n"/>
+      <c r="G31" s="24" t="n"/>
+      <c r="H31" s="24" t="n"/>
+      <c r="I31" s="24" t="n"/>
+      <c r="J31" s="25" t="n"/>
+      <c r="K31" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="63" t="n"/>
+      <c r="M31" s="63" t="n"/>
+      <c r="N31" s="63" t="n"/>
+      <c r="O31" s="63" t="n"/>
+      <c r="P31" s="66" t="n"/>
+      <c r="Q31" s="67" t="n"/>
+      <c r="R31" s="44" t="n"/>
+      <c r="S31" s="44" t="n"/>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="78" t="inlineStr">
+        <is>
+          <t>Running:   44 line-years × $500,000</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="n"/>
+      <c r="C32" s="24" t="n"/>
+      <c r="D32" s="24" t="n"/>
+      <c r="E32" s="24" t="n"/>
+      <c r="F32" s="24" t="n"/>
+      <c r="G32" s="24" t="n"/>
+      <c r="H32" s="24" t="n"/>
+      <c r="I32" s="24" t="n"/>
+      <c r="J32" s="25" t="n"/>
+      <c r="K32" s="79" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="L32" s="63" t="n"/>
+      <c r="M32" s="63" t="n"/>
+      <c r="N32" s="63" t="n"/>
+      <c r="O32" s="63" t="n"/>
+      <c r="P32" s="66" t="n"/>
+      <c r="Q32" s="67" t="n"/>
+      <c r="R32" s="44" t="n"/>
+      <c r="S32" s="44" t="n"/>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="78" t="inlineStr">
+        <is>
+          <t>Late intros: 0 × $600,000</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="n"/>
+      <c r="C33" s="24" t="n"/>
+      <c r="D33" s="24" t="n"/>
+      <c r="E33" s="24" t="n"/>
+      <c r="F33" s="24" t="n"/>
+      <c r="G33" s="24" t="n"/>
+      <c r="H33" s="24" t="n"/>
+      <c r="I33" s="24" t="n"/>
+      <c r="J33" s="25" t="n"/>
+      <c r="K33" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="63" t="n"/>
+      <c r="M33" s="63" t="n"/>
+      <c r="N33" s="63" t="n"/>
+      <c r="O33" s="63" t="n"/>
+      <c r="P33" s="66" t="n"/>
+      <c r="Q33" s="67" t="n"/>
+      <c r="R33" s="44" t="n"/>
+      <c r="S33" s="44" t="n"/>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="78" t="inlineStr">
+        <is>
+          <t>Mech tooling: 12 sets × $110,000</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="n"/>
+      <c r="C34" s="24" t="n"/>
+      <c r="D34" s="24" t="n"/>
+      <c r="E34" s="24" t="n"/>
+      <c r="F34" s="24" t="n"/>
+      <c r="G34" s="24" t="n"/>
+      <c r="H34" s="24" t="n"/>
+      <c r="I34" s="24" t="n"/>
+      <c r="J34" s="25" t="n"/>
+      <c r="K34" s="79" t="n">
+        <v>1320000</v>
+      </c>
+      <c r="L34" s="63" t="n"/>
+      <c r="M34" s="63" t="n"/>
+      <c r="N34" s="63" t="n"/>
+      <c r="O34" s="63" t="n"/>
+      <c r="P34" s="66" t="n"/>
+      <c r="Q34" s="67" t="n"/>
+      <c r="R34" s="44" t="n"/>
+      <c r="S34" s="44" t="n"/>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="78" t="inlineStr">
+        <is>
+          <t>Opt tooling:  12 sets × $220,000</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="n"/>
+      <c r="C35" s="24" t="n"/>
+      <c r="D35" s="24" t="n"/>
+      <c r="E35" s="24" t="n"/>
+      <c r="F35" s="24" t="n"/>
+      <c r="G35" s="24" t="n"/>
+      <c r="H35" s="24" t="n"/>
+      <c r="I35" s="24" t="n"/>
+      <c r="J35" s="25" t="n"/>
+      <c r="K35" s="79" t="n">
+        <v>2640000</v>
+      </c>
+      <c r="L35" s="63" t="n"/>
+      <c r="M35" s="63" t="n"/>
+      <c r="N35" s="63" t="n"/>
+      <c r="O35" s="63" t="n"/>
+      <c r="P35" s="66" t="n"/>
+      <c r="Q35" s="67" t="n"/>
+      <c r="R35" s="44" t="n"/>
+      <c r="S35" s="44" t="n"/>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="59" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="n"/>
+      <c r="C36" s="24" t="n"/>
+      <c r="D36" s="24" t="n"/>
+      <c r="E36" s="24" t="n"/>
+      <c r="F36" s="24" t="n"/>
+      <c r="G36" s="24" t="n"/>
+      <c r="H36" s="24" t="n"/>
+      <c r="I36" s="24" t="n"/>
+      <c r="J36" s="25" t="n"/>
+      <c r="K36" s="80" t="n">
+        <v>25960000</v>
+      </c>
+      <c r="L36" s="63" t="n"/>
+      <c r="M36" s="63" t="n"/>
+      <c r="N36" s="63" t="n"/>
+      <c r="O36" s="63" t="n"/>
+      <c r="P36" s="66" t="n"/>
+      <c r="Q36" s="67" t="n"/>
+      <c r="R36" s="44" t="n"/>
+      <c r="S36" s="44" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="38" t="n">
-        <v>2037</v>
-      </c>
-      <c r="B37" s="39" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="C37" s="39" t="n">
-        <v>2035</v>
-      </c>
-      <c r="D37" s="40" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E37" s="41" t="n"/>
-      <c r="F37" s="41" t="n">
-        <v>1530317</v>
-      </c>
-      <c r="G37" s="41" t="n"/>
-      <c r="H37" s="41" t="n"/>
-      <c r="I37" s="41" t="n"/>
-      <c r="J37" s="41" t="n"/>
-      <c r="K37" s="41" t="n"/>
-      <c r="L37" s="41" t="n"/>
-      <c r="M37" s="41" t="n"/>
-      <c r="N37" s="41" t="n"/>
-      <c r="O37" s="41" t="n">
-        <v>1530317</v>
-      </c>
-      <c r="P37" s="42" t="n">
-        <v>82</v>
-      </c>
-      <c r="Q37" s="43" t="n">
-        <v>85</v>
-      </c>
+      <c r="A37" s="73" t="n"/>
+      <c r="B37" s="61" t="n"/>
+      <c r="C37" s="61" t="n"/>
+      <c r="D37" s="62" t="n"/>
+      <c r="E37" s="63" t="n"/>
+      <c r="F37" s="63" t="n"/>
+      <c r="G37" s="63" t="n"/>
+      <c r="H37" s="63" t="n"/>
+      <c r="I37" s="63" t="n"/>
+      <c r="J37" s="63" t="n"/>
+      <c r="K37" s="63" t="n"/>
+      <c r="L37" s="63" t="n"/>
+      <c r="M37" s="63" t="n"/>
+      <c r="N37" s="63" t="n"/>
+      <c r="O37" s="63" t="n"/>
+      <c r="P37" s="66" t="n"/>
+      <c r="Q37" s="67" t="n"/>
+      <c r="R37" s="44" t="n"/>
+      <c r="S37" s="44" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="32" t="n">
-        <v>2037</v>
-      </c>
-      <c r="B38" s="33" t="inlineStr">
-        <is>
-          <t>L5</t>
-        </is>
-      </c>
-      <c r="C38" s="33" t="n">
-        <v>2034</v>
-      </c>
-      <c r="D38" s="34" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E38" s="35" t="n"/>
-      <c r="F38" s="35" t="n">
-        <v>910631</v>
-      </c>
-      <c r="G38" s="35" t="n"/>
-      <c r="H38" s="35" t="n"/>
-      <c r="I38" s="35" t="n"/>
-      <c r="J38" s="35" t="n"/>
-      <c r="K38" s="35" t="n"/>
-      <c r="L38" s="35" t="n"/>
-      <c r="M38" s="35" t="n"/>
-      <c r="N38" s="35" t="n"/>
-      <c r="O38" s="35" t="n">
-        <v>910631</v>
-      </c>
-      <c r="P38" s="36" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="Q38" s="37" t="n">
-        <v>85</v>
-      </c>
+      <c r="A38" s="73" t="n"/>
+      <c r="B38" s="61" t="n"/>
+      <c r="C38" s="61" t="n"/>
+      <c r="D38" s="62" t="n"/>
+      <c r="E38" s="63" t="n"/>
+      <c r="F38" s="63" t="n"/>
+      <c r="G38" s="63" t="n"/>
+      <c r="H38" s="63" t="n"/>
+      <c r="I38" s="63" t="n"/>
+      <c r="J38" s="63" t="n"/>
+      <c r="K38" s="63" t="n"/>
+      <c r="L38" s="63" t="n"/>
+      <c r="M38" s="63" t="n"/>
+      <c r="N38" s="63" t="n"/>
+      <c r="O38" s="63" t="n"/>
+      <c r="P38" s="66" t="n"/>
+      <c r="Q38" s="67" t="n"/>
+      <c r="R38" s="44" t="n"/>
+      <c r="S38" s="44" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="38" t="n">
-        <v>2037</v>
-      </c>
-      <c r="B39" s="39" t="inlineStr">
-        <is>
-          <t>L6</t>
-        </is>
-      </c>
-      <c r="C39" s="39" t="n">
-        <v>2035</v>
-      </c>
-      <c r="D39" s="40" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="E39" s="41" t="n"/>
-      <c r="F39" s="41" t="n"/>
-      <c r="G39" s="41" t="n">
-        <v>610237</v>
-      </c>
-      <c r="H39" s="41" t="n"/>
-      <c r="I39" s="41" t="n"/>
-      <c r="J39" s="41" t="n"/>
-      <c r="K39" s="41" t="n"/>
-      <c r="L39" s="41" t="n"/>
-      <c r="M39" s="41" t="n"/>
-      <c r="N39" s="41" t="n"/>
-      <c r="O39" s="41" t="n">
-        <v>610237</v>
-      </c>
-      <c r="P39" s="42" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="Q39" s="43" t="n">
-        <v>85</v>
-      </c>
+      <c r="A39" s="73" t="n"/>
+      <c r="B39" s="61" t="n"/>
+      <c r="C39" s="61" t="n"/>
+      <c r="D39" s="62" t="n"/>
+      <c r="E39" s="63" t="n"/>
+      <c r="F39" s="63" t="n"/>
+      <c r="G39" s="63" t="n"/>
+      <c r="H39" s="63" t="n"/>
+      <c r="I39" s="63" t="n"/>
+      <c r="J39" s="63" t="n"/>
+      <c r="K39" s="63" t="n"/>
+      <c r="L39" s="63" t="n"/>
+      <c r="M39" s="63" t="n"/>
+      <c r="N39" s="63" t="n"/>
+      <c r="O39" s="63" t="n"/>
+      <c r="P39" s="66" t="n"/>
+      <c r="Q39" s="67" t="n"/>
+      <c r="R39" s="44" t="n"/>
+      <c r="S39" s="44" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="32" t="n">
-        <v>2037</v>
-      </c>
-      <c r="B40" s="33" t="inlineStr">
-        <is>
-          <t>L7</t>
-        </is>
-      </c>
-      <c r="C40" s="33" t="n">
-        <v>2033</v>
-      </c>
-      <c r="D40" s="34" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E40" s="35" t="n">
-        <v>610237</v>
-      </c>
-      <c r="F40" s="35" t="n"/>
-      <c r="G40" s="35" t="n"/>
-      <c r="H40" s="35" t="n"/>
-      <c r="I40" s="35" t="n"/>
-      <c r="J40" s="35" t="n"/>
-      <c r="K40" s="35" t="n"/>
-      <c r="L40" s="35" t="n"/>
-      <c r="M40" s="35" t="n"/>
-      <c r="N40" s="35" t="n"/>
-      <c r="O40" s="35" t="n">
-        <v>610237</v>
-      </c>
-      <c r="P40" s="36" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="Q40" s="37" t="n">
-        <v>85</v>
-      </c>
+      <c r="A40" s="73" t="n"/>
+      <c r="B40" s="61" t="n"/>
+      <c r="C40" s="61" t="n"/>
+      <c r="D40" s="62" t="n"/>
+      <c r="E40" s="63" t="n"/>
+      <c r="F40" s="63" t="n"/>
+      <c r="G40" s="63" t="n"/>
+      <c r="H40" s="63" t="n"/>
+      <c r="I40" s="63" t="n"/>
+      <c r="J40" s="63" t="n"/>
+      <c r="K40" s="63" t="n"/>
+      <c r="L40" s="63" t="n"/>
+      <c r="M40" s="63" t="n"/>
+      <c r="N40" s="63" t="n"/>
+      <c r="O40" s="63" t="n"/>
+      <c r="P40" s="66" t="n"/>
+      <c r="Q40" s="67" t="n"/>
+      <c r="R40" s="44" t="n"/>
+      <c r="S40" s="44" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="38" t="n">
-        <v>2038</v>
-      </c>
-      <c r="B41" s="39" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="C41" s="39" t="n">
-        <v>2029</v>
-      </c>
-      <c r="D41" s="40" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="E41" s="41" t="n"/>
-      <c r="F41" s="41" t="n"/>
-      <c r="G41" s="41" t="n"/>
-      <c r="H41" s="41" t="n">
-        <v>173752</v>
-      </c>
-      <c r="I41" s="41" t="n"/>
-      <c r="J41" s="41" t="n"/>
-      <c r="K41" s="41" t="n"/>
-      <c r="L41" s="41" t="n"/>
-      <c r="M41" s="41" t="n"/>
-      <c r="N41" s="41" t="n"/>
-      <c r="O41" s="41" t="n">
-        <v>173752</v>
-      </c>
-      <c r="P41" s="42" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Q41" s="43" t="n">
-        <v>85</v>
-      </c>
+      <c r="A41" s="73" t="n"/>
+      <c r="B41" s="61" t="n"/>
+      <c r="C41" s="61" t="n"/>
+      <c r="D41" s="62" t="n"/>
+      <c r="E41" s="63" t="n"/>
+      <c r="F41" s="63" t="n"/>
+      <c r="G41" s="63" t="n"/>
+      <c r="H41" s="63" t="n"/>
+      <c r="I41" s="63" t="n"/>
+      <c r="J41" s="63" t="n"/>
+      <c r="K41" s="63" t="n"/>
+      <c r="L41" s="63" t="n"/>
+      <c r="M41" s="63" t="n"/>
+      <c r="N41" s="63" t="n"/>
+      <c r="O41" s="63" t="n"/>
+      <c r="P41" s="66" t="n"/>
+      <c r="Q41" s="67" t="n"/>
+      <c r="R41" s="44" t="n"/>
+      <c r="S41" s="44" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="32" t="n">
-        <v>2038</v>
-      </c>
-      <c r="B42" s="33" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="C42" s="33" t="n">
-        <v>2035</v>
-      </c>
-      <c r="D42" s="34" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E42" s="35" t="n"/>
-      <c r="F42" s="35" t="n">
-        <v>695008</v>
-      </c>
-      <c r="G42" s="35" t="n"/>
-      <c r="H42" s="35" t="n"/>
-      <c r="I42" s="35" t="n"/>
-      <c r="J42" s="35" t="n"/>
-      <c r="K42" s="35" t="n"/>
-      <c r="L42" s="35" t="n"/>
-      <c r="M42" s="35" t="n"/>
-      <c r="N42" s="35" t="n"/>
-      <c r="O42" s="35" t="n">
-        <v>695008</v>
-      </c>
-      <c r="P42" s="36" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="Q42" s="37" t="n">
-        <v>85</v>
-      </c>
+      <c r="A42" s="73" t="n"/>
+      <c r="B42" s="61" t="n"/>
+      <c r="C42" s="61" t="n"/>
+      <c r="D42" s="62" t="n"/>
+      <c r="E42" s="63" t="n"/>
+      <c r="F42" s="63" t="n"/>
+      <c r="G42" s="63" t="n"/>
+      <c r="H42" s="63" t="n"/>
+      <c r="I42" s="63" t="n"/>
+      <c r="J42" s="63" t="n"/>
+      <c r="K42" s="63" t="n"/>
+      <c r="L42" s="63" t="n"/>
+      <c r="M42" s="63" t="n"/>
+      <c r="N42" s="63" t="n"/>
+      <c r="O42" s="63" t="n"/>
+      <c r="P42" s="66" t="n"/>
+      <c r="Q42" s="67" t="n"/>
+      <c r="R42" s="44" t="n"/>
+      <c r="S42" s="44" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="38" t="n">
-        <v>2038</v>
-      </c>
-      <c r="B43" s="39" t="inlineStr">
-        <is>
-          <t>L6</t>
-        </is>
-      </c>
-      <c r="C43" s="39" t="n">
-        <v>2035</v>
-      </c>
-      <c r="D43" s="40" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="E43" s="41" t="n"/>
-      <c r="F43" s="41" t="n"/>
-      <c r="G43" s="41" t="n">
-        <v>173752</v>
-      </c>
-      <c r="H43" s="41" t="n"/>
-      <c r="I43" s="41" t="n"/>
-      <c r="J43" s="41" t="n"/>
-      <c r="K43" s="41" t="n"/>
-      <c r="L43" s="41" t="n"/>
-      <c r="M43" s="41" t="n"/>
-      <c r="N43" s="41" t="n"/>
-      <c r="O43" s="41" t="n">
-        <v>173752</v>
-      </c>
-      <c r="P43" s="42" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Q43" s="43" t="n">
-        <v>85</v>
-      </c>
+      <c r="A43" s="73" t="n"/>
+      <c r="B43" s="61" t="n"/>
+      <c r="C43" s="61" t="n"/>
+      <c r="D43" s="62" t="n"/>
+      <c r="E43" s="63" t="n"/>
+      <c r="F43" s="63" t="n"/>
+      <c r="G43" s="63" t="n"/>
+      <c r="H43" s="63" t="n"/>
+      <c r="I43" s="63" t="n"/>
+      <c r="J43" s="63" t="n"/>
+      <c r="K43" s="63" t="n"/>
+      <c r="L43" s="63" t="n"/>
+      <c r="M43" s="63" t="n"/>
+      <c r="N43" s="63" t="n"/>
+      <c r="O43" s="63" t="n"/>
+      <c r="P43" s="66" t="n"/>
+      <c r="Q43" s="67" t="n"/>
+      <c r="R43" s="44" t="n"/>
+      <c r="S43" s="44" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="32" t="n">
-        <v>2038</v>
-      </c>
-      <c r="B44" s="33" t="inlineStr">
-        <is>
-          <t>L7</t>
-        </is>
-      </c>
-      <c r="C44" s="33" t="n">
-        <v>2033</v>
-      </c>
-      <c r="D44" s="34" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E44" s="35" t="n">
-        <v>173752</v>
-      </c>
-      <c r="F44" s="35" t="n"/>
-      <c r="G44" s="35" t="n"/>
-      <c r="H44" s="35" t="n"/>
-      <c r="I44" s="35" t="n"/>
-      <c r="J44" s="35" t="n"/>
-      <c r="K44" s="35" t="n"/>
-      <c r="L44" s="35" t="n"/>
-      <c r="M44" s="35" t="n"/>
-      <c r="N44" s="35" t="n"/>
-      <c r="O44" s="35" t="n">
-        <v>173752</v>
-      </c>
-      <c r="P44" s="36" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Q44" s="37" t="n">
-        <v>85</v>
-      </c>
+      <c r="A44" s="73" t="n"/>
+      <c r="B44" s="61" t="n"/>
+      <c r="C44" s="61" t="n"/>
+      <c r="D44" s="62" t="n"/>
+      <c r="E44" s="63" t="n"/>
+      <c r="F44" s="63" t="n"/>
+      <c r="G44" s="63" t="n"/>
+      <c r="H44" s="63" t="n"/>
+      <c r="I44" s="63" t="n"/>
+      <c r="J44" s="63" t="n"/>
+      <c r="K44" s="63" t="n"/>
+      <c r="L44" s="63" t="n"/>
+      <c r="M44" s="63" t="n"/>
+      <c r="N44" s="63" t="n"/>
+      <c r="O44" s="63" t="n"/>
+      <c r="P44" s="66" t="n"/>
+      <c r="Q44" s="67" t="n"/>
+      <c r="R44" s="44" t="n"/>
+      <c r="S44" s="44" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="44" t="n"/>
@@ -5640,6 +5436,8 @@
       <c r="O45" s="44" t="n"/>
       <c r="P45" s="44" t="n"/>
       <c r="Q45" s="44" t="n"/>
+      <c r="R45" s="44" t="n"/>
+      <c r="S45" s="44" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="44" t="n"/>
@@ -5659,6 +5457,8 @@
       <c r="O46" s="44" t="n"/>
       <c r="P46" s="44" t="n"/>
       <c r="Q46" s="44" t="n"/>
+      <c r="R46" s="44" t="n"/>
+      <c r="S46" s="44" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="44" t="n"/>
@@ -5678,6 +5478,8 @@
       <c r="O47" s="44" t="n"/>
       <c r="P47" s="44" t="n"/>
       <c r="Q47" s="44" t="n"/>
+      <c r="R47" s="44" t="n"/>
+      <c r="S47" s="44" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="44" t="n"/>
@@ -5697,6 +5499,8 @@
       <c r="O48" s="44" t="n"/>
       <c r="P48" s="44" t="n"/>
       <c r="Q48" s="44" t="n"/>
+      <c r="R48" s="44" t="n"/>
+      <c r="S48" s="44" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="44" t="n"/>
@@ -5716,6 +5520,8 @@
       <c r="O49" s="44" t="n"/>
       <c r="P49" s="44" t="n"/>
       <c r="Q49" s="44" t="n"/>
+      <c r="R49" s="44" t="n"/>
+      <c r="S49" s="44" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="44" t="n"/>
@@ -5735,6 +5541,8 @@
       <c r="O50" s="44" t="n"/>
       <c r="P50" s="44" t="n"/>
       <c r="Q50" s="44" t="n"/>
+      <c r="R50" s="44" t="n"/>
+      <c r="S50" s="44" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="44" t="n"/>
@@ -5754,6 +5562,8 @@
       <c r="O51" s="44" t="n"/>
       <c r="P51" s="44" t="n"/>
       <c r="Q51" s="44" t="n"/>
+      <c r="R51" s="44" t="n"/>
+      <c r="S51" s="44" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="44" t="n"/>
@@ -5773,6 +5583,8 @@
       <c r="O52" s="44" t="n"/>
       <c r="P52" s="44" t="n"/>
       <c r="Q52" s="44" t="n"/>
+      <c r="R52" s="44" t="n"/>
+      <c r="S52" s="44" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="44" t="n"/>
@@ -5792,6 +5604,8 @@
       <c r="O53" s="44" t="n"/>
       <c r="P53" s="44" t="n"/>
       <c r="Q53" s="44" t="n"/>
+      <c r="R53" s="44" t="n"/>
+      <c r="S53" s="44" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="44" t="n"/>
@@ -5811,6 +5625,8 @@
       <c r="O54" s="44" t="n"/>
       <c r="P54" s="44" t="n"/>
       <c r="Q54" s="44" t="n"/>
+      <c r="R54" s="44" t="n"/>
+      <c r="S54" s="44" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="44" t="n"/>
@@ -5830,6 +5646,8 @@
       <c r="O55" s="44" t="n"/>
       <c r="P55" s="44" t="n"/>
       <c r="Q55" s="44" t="n"/>
+      <c r="R55" s="44" t="n"/>
+      <c r="S55" s="44" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="44" t="n"/>
@@ -5849,6 +5667,8 @@
       <c r="O56" s="44" t="n"/>
       <c r="P56" s="44" t="n"/>
       <c r="Q56" s="44" t="n"/>
+      <c r="R56" s="44" t="n"/>
+      <c r="S56" s="44" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="44" t="n"/>
@@ -5868,6 +5688,8 @@
       <c r="O57" s="44" t="n"/>
       <c r="P57" s="44" t="n"/>
       <c r="Q57" s="44" t="n"/>
+      <c r="R57" s="44" t="n"/>
+      <c r="S57" s="44" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="44" t="n"/>
@@ -5887,6 +5709,8 @@
       <c r="O58" s="44" t="n"/>
       <c r="P58" s="44" t="n"/>
       <c r="Q58" s="44" t="n"/>
+      <c r="R58" s="44" t="n"/>
+      <c r="S58" s="44" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="44" t="n"/>
@@ -5906,6 +5730,8 @@
       <c r="O59" s="44" t="n"/>
       <c r="P59" s="44" t="n"/>
       <c r="Q59" s="44" t="n"/>
+      <c r="R59" s="44" t="n"/>
+      <c r="S59" s="44" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="44" t="n"/>
@@ -5925,6 +5751,8 @@
       <c r="O60" s="44" t="n"/>
       <c r="P60" s="44" t="n"/>
       <c r="Q60" s="44" t="n"/>
+      <c r="R60" s="44" t="n"/>
+      <c r="S60" s="44" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="44" t="n"/>
@@ -5944,6 +5772,8 @@
       <c r="O61" s="44" t="n"/>
       <c r="P61" s="44" t="n"/>
       <c r="Q61" s="44" t="n"/>
+      <c r="R61" s="44" t="n"/>
+      <c r="S61" s="44" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="44" t="n"/>
@@ -5963,6 +5793,8 @@
       <c r="O62" s="44" t="n"/>
       <c r="P62" s="44" t="n"/>
       <c r="Q62" s="44" t="n"/>
+      <c r="R62" s="44" t="n"/>
+      <c r="S62" s="44" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="44" t="n"/>
@@ -5982,6 +5814,8 @@
       <c r="O63" s="44" t="n"/>
       <c r="P63" s="44" t="n"/>
       <c r="Q63" s="44" t="n"/>
+      <c r="R63" s="44" t="n"/>
+      <c r="S63" s="44" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="44" t="n"/>
@@ -6001,6 +5835,8 @@
       <c r="O64" s="44" t="n"/>
       <c r="P64" s="44" t="n"/>
       <c r="Q64" s="44" t="n"/>
+      <c r="R64" s="44" t="n"/>
+      <c r="S64" s="44" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="44" t="n"/>
@@ -6020,6 +5856,8 @@
       <c r="O65" s="44" t="n"/>
       <c r="P65" s="44" t="n"/>
       <c r="Q65" s="44" t="n"/>
+      <c r="R65" s="44" t="n"/>
+      <c r="S65" s="44" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="44" t="n"/>
@@ -6039,6 +5877,8 @@
       <c r="O66" s="44" t="n"/>
       <c r="P66" s="44" t="n"/>
       <c r="Q66" s="44" t="n"/>
+      <c r="R66" s="44" t="n"/>
+      <c r="S66" s="44" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="44" t="n"/>
@@ -6058,6 +5898,8 @@
       <c r="O67" s="44" t="n"/>
       <c r="P67" s="44" t="n"/>
       <c r="Q67" s="44" t="n"/>
+      <c r="R67" s="44" t="n"/>
+      <c r="S67" s="44" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="44" t="n"/>
@@ -6077,6 +5919,8 @@
       <c r="O68" s="44" t="n"/>
       <c r="P68" s="44" t="n"/>
       <c r="Q68" s="44" t="n"/>
+      <c r="R68" s="44" t="n"/>
+      <c r="S68" s="44" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="44" t="n"/>
@@ -6096,6 +5940,8 @@
       <c r="O69" s="44" t="n"/>
       <c r="P69" s="44" t="n"/>
       <c r="Q69" s="44" t="n"/>
+      <c r="R69" s="44" t="n"/>
+      <c r="S69" s="44" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="44" t="n"/>
@@ -6115,6 +5961,8 @@
       <c r="O70" s="44" t="n"/>
       <c r="P70" s="44" t="n"/>
       <c r="Q70" s="44" t="n"/>
+      <c r="R70" s="44" t="n"/>
+      <c r="S70" s="44" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="44" t="n"/>
@@ -6134,6 +5982,8 @@
       <c r="O71" s="44" t="n"/>
       <c r="P71" s="44" t="n"/>
       <c r="Q71" s="44" t="n"/>
+      <c r="R71" s="44" t="n"/>
+      <c r="S71" s="44" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="44" t="n"/>
@@ -6153,6 +6003,8 @@
       <c r="O72" s="44" t="n"/>
       <c r="P72" s="44" t="n"/>
       <c r="Q72" s="44" t="n"/>
+      <c r="R72" s="44" t="n"/>
+      <c r="S72" s="44" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="44" t="n"/>
@@ -6172,6 +6024,8 @@
       <c r="O73" s="44" t="n"/>
       <c r="P73" s="44" t="n"/>
       <c r="Q73" s="44" t="n"/>
+      <c r="R73" s="44" t="n"/>
+      <c r="S73" s="44" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="44" t="n"/>
@@ -6191,6 +6045,8 @@
       <c r="O74" s="44" t="n"/>
       <c r="P74" s="44" t="n"/>
       <c r="Q74" s="44" t="n"/>
+      <c r="R74" s="44" t="n"/>
+      <c r="S74" s="44" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="44" t="n"/>
@@ -6210,6 +6066,8 @@
       <c r="O75" s="44" t="n"/>
       <c r="P75" s="44" t="n"/>
       <c r="Q75" s="44" t="n"/>
+      <c r="R75" s="44" t="n"/>
+      <c r="S75" s="44" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="44" t="n"/>
@@ -6229,6 +6087,8 @@
       <c r="O76" s="44" t="n"/>
       <c r="P76" s="44" t="n"/>
       <c r="Q76" s="44" t="n"/>
+      <c r="R76" s="44" t="n"/>
+      <c r="S76" s="44" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="44" t="n"/>
@@ -6248,6 +6108,8 @@
       <c r="O77" s="44" t="n"/>
       <c r="P77" s="44" t="n"/>
       <c r="Q77" s="44" t="n"/>
+      <c r="R77" s="44" t="n"/>
+      <c r="S77" s="44" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="44" t="n"/>
@@ -6267,6 +6129,8 @@
       <c r="O78" s="44" t="n"/>
       <c r="P78" s="44" t="n"/>
       <c r="Q78" s="44" t="n"/>
+      <c r="R78" s="44" t="n"/>
+      <c r="S78" s="44" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="44" t="n"/>
@@ -6286,6 +6150,8 @@
       <c r="O79" s="44" t="n"/>
       <c r="P79" s="44" t="n"/>
       <c r="Q79" s="44" t="n"/>
+      <c r="R79" s="44" t="n"/>
+      <c r="S79" s="44" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="44" t="n"/>
@@ -6305,6 +6171,8 @@
       <c r="O80" s="44" t="n"/>
       <c r="P80" s="44" t="n"/>
       <c r="Q80" s="44" t="n"/>
+      <c r="R80" s="44" t="n"/>
+      <c r="S80" s="44" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="44" t="n"/>
@@ -6324,6 +6192,8 @@
       <c r="O81" s="44" t="n"/>
       <c r="P81" s="44" t="n"/>
       <c r="Q81" s="44" t="n"/>
+      <c r="R81" s="44" t="n"/>
+      <c r="S81" s="44" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="44" t="n"/>
@@ -6343,6 +6213,8 @@
       <c r="O82" s="44" t="n"/>
       <c r="P82" s="44" t="n"/>
       <c r="Q82" s="44" t="n"/>
+      <c r="R82" s="44" t="n"/>
+      <c r="S82" s="44" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="44" t="n"/>
@@ -6362,6 +6234,8 @@
       <c r="O83" s="44" t="n"/>
       <c r="P83" s="44" t="n"/>
       <c r="Q83" s="44" t="n"/>
+      <c r="R83" s="44" t="n"/>
+      <c r="S83" s="44" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="44" t="n"/>
@@ -6381,6 +6255,8 @@
       <c r="O84" s="44" t="n"/>
       <c r="P84" s="44" t="n"/>
       <c r="Q84" s="44" t="n"/>
+      <c r="R84" s="44" t="n"/>
+      <c r="S84" s="44" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="44" t="n"/>
@@ -6400,6 +6276,8 @@
       <c r="O85" s="44" t="n"/>
       <c r="P85" s="44" t="n"/>
       <c r="Q85" s="44" t="n"/>
+      <c r="R85" s="44" t="n"/>
+      <c r="S85" s="44" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="44" t="n"/>
@@ -6419,6 +6297,8 @@
       <c r="O86" s="44" t="n"/>
       <c r="P86" s="44" t="n"/>
       <c r="Q86" s="44" t="n"/>
+      <c r="R86" s="44" t="n"/>
+      <c r="S86" s="44" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="44" t="n"/>
@@ -6438,6 +6318,8 @@
       <c r="O87" s="44" t="n"/>
       <c r="P87" s="44" t="n"/>
       <c r="Q87" s="44" t="n"/>
+      <c r="R87" s="44" t="n"/>
+      <c r="S87" s="44" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="44" t="n"/>
@@ -6457,6 +6339,8 @@
       <c r="O88" s="44" t="n"/>
       <c r="P88" s="44" t="n"/>
       <c r="Q88" s="44" t="n"/>
+      <c r="R88" s="44" t="n"/>
+      <c r="S88" s="44" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="44" t="n"/>
@@ -6476,6 +6360,8 @@
       <c r="O89" s="44" t="n"/>
       <c r="P89" s="44" t="n"/>
       <c r="Q89" s="44" t="n"/>
+      <c r="R89" s="44" t="n"/>
+      <c r="S89" s="44" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="44" t="n"/>
@@ -6495,6 +6381,8 @@
       <c r="O90" s="44" t="n"/>
       <c r="P90" s="44" t="n"/>
       <c r="Q90" s="44" t="n"/>
+      <c r="R90" s="44" t="n"/>
+      <c r="S90" s="44" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="44" t="n"/>
@@ -6514,6 +6402,8 @@
       <c r="O91" s="44" t="n"/>
       <c r="P91" s="44" t="n"/>
       <c r="Q91" s="44" t="n"/>
+      <c r="R91" s="44" t="n"/>
+      <c r="S91" s="44" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="44" t="n"/>
@@ -6533,6 +6423,8 @@
       <c r="O92" s="44" t="n"/>
       <c r="P92" s="44" t="n"/>
       <c r="Q92" s="44" t="n"/>
+      <c r="R92" s="44" t="n"/>
+      <c r="S92" s="44" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="44" t="n"/>
@@ -6552,6 +6444,8 @@
       <c r="O93" s="44" t="n"/>
       <c r="P93" s="44" t="n"/>
       <c r="Q93" s="44" t="n"/>
+      <c r="R93" s="44" t="n"/>
+      <c r="S93" s="44" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="44" t="n"/>
@@ -6571,6 +6465,8 @@
       <c r="O94" s="44" t="n"/>
       <c r="P94" s="44" t="n"/>
       <c r="Q94" s="44" t="n"/>
+      <c r="R94" s="44" t="n"/>
+      <c r="S94" s="44" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="44" t="n"/>
@@ -6590,6 +6486,8 @@
       <c r="O95" s="44" t="n"/>
       <c r="P95" s="44" t="n"/>
       <c r="Q95" s="44" t="n"/>
+      <c r="R95" s="44" t="n"/>
+      <c r="S95" s="44" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="44" t="n"/>
@@ -6609,6 +6507,8 @@
       <c r="O96" s="44" t="n"/>
       <c r="P96" s="44" t="n"/>
       <c r="Q96" s="44" t="n"/>
+      <c r="R96" s="44" t="n"/>
+      <c r="S96" s="44" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="44" t="n"/>
@@ -6628,6 +6528,8 @@
       <c r="O97" s="44" t="n"/>
       <c r="P97" s="44" t="n"/>
       <c r="Q97" s="44" t="n"/>
+      <c r="R97" s="44" t="n"/>
+      <c r="S97" s="44" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="44" t="n"/>
@@ -6647,6 +6549,8 @@
       <c r="O98" s="44" t="n"/>
       <c r="P98" s="44" t="n"/>
       <c r="Q98" s="44" t="n"/>
+      <c r="R98" s="44" t="n"/>
+      <c r="S98" s="44" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="44" t="n"/>
@@ -6666,6 +6570,8 @@
       <c r="O99" s="44" t="n"/>
       <c r="P99" s="44" t="n"/>
       <c r="Q99" s="44" t="n"/>
+      <c r="R99" s="44" t="n"/>
+      <c r="S99" s="44" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="44" t="n"/>
@@ -6685,6 +6591,8 @@
       <c r="O100" s="44" t="n"/>
       <c r="P100" s="44" t="n"/>
       <c r="Q100" s="44" t="n"/>
+      <c r="R100" s="44" t="n"/>
+      <c r="S100" s="44" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="44" t="n"/>
@@ -6704,6 +6612,8 @@
       <c r="O101" s="44" t="n"/>
       <c r="P101" s="44" t="n"/>
       <c r="Q101" s="44" t="n"/>
+      <c r="R101" s="44" t="n"/>
+      <c r="S101" s="44" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="44" t="n"/>
@@ -6723,6 +6633,8 @@
       <c r="O102" s="44" t="n"/>
       <c r="P102" s="44" t="n"/>
       <c r="Q102" s="44" t="n"/>
+      <c r="R102" s="44" t="n"/>
+      <c r="S102" s="44" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="44" t="n"/>
@@ -6742,6 +6654,8 @@
       <c r="O103" s="44" t="n"/>
       <c r="P103" s="44" t="n"/>
       <c r="Q103" s="44" t="n"/>
+      <c r="R103" s="44" t="n"/>
+      <c r="S103" s="44" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="44" t="n"/>
@@ -6761,6 +6675,8 @@
       <c r="O104" s="44" t="n"/>
       <c r="P104" s="44" t="n"/>
       <c r="Q104" s="44" t="n"/>
+      <c r="R104" s="44" t="n"/>
+      <c r="S104" s="44" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="44" t="n"/>
@@ -6780,6 +6696,8 @@
       <c r="O105" s="44" t="n"/>
       <c r="P105" s="44" t="n"/>
       <c r="Q105" s="44" t="n"/>
+      <c r="R105" s="44" t="n"/>
+      <c r="S105" s="44" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="44" t="n"/>
@@ -6799,6 +6717,8 @@
       <c r="O106" s="44" t="n"/>
       <c r="P106" s="44" t="n"/>
       <c r="Q106" s="44" t="n"/>
+      <c r="R106" s="44" t="n"/>
+      <c r="S106" s="44" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="44" t="n"/>
@@ -6818,6 +6738,8 @@
       <c r="O107" s="44" t="n"/>
       <c r="P107" s="44" t="n"/>
       <c r="Q107" s="44" t="n"/>
+      <c r="R107" s="44" t="n"/>
+      <c r="S107" s="44" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="44" t="n"/>
@@ -6837,6 +6759,8 @@
       <c r="O108" s="44" t="n"/>
       <c r="P108" s="44" t="n"/>
       <c r="Q108" s="44" t="n"/>
+      <c r="R108" s="44" t="n"/>
+      <c r="S108" s="44" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="44" t="n"/>
@@ -6856,6 +6780,8 @@
       <c r="O109" s="44" t="n"/>
       <c r="P109" s="44" t="n"/>
       <c r="Q109" s="44" t="n"/>
+      <c r="R109" s="44" t="n"/>
+      <c r="S109" s="44" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="44" t="n"/>
@@ -6875,6 +6801,8 @@
       <c r="O110" s="44" t="n"/>
       <c r="P110" s="44" t="n"/>
       <c r="Q110" s="44" t="n"/>
+      <c r="R110" s="44" t="n"/>
+      <c r="S110" s="44" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="44" t="n"/>
@@ -6894,6 +6822,8 @@
       <c r="O111" s="44" t="n"/>
       <c r="P111" s="44" t="n"/>
       <c r="Q111" s="44" t="n"/>
+      <c r="R111" s="44" t="n"/>
+      <c r="S111" s="44" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="44" t="n"/>
@@ -6913,6 +6843,8 @@
       <c r="O112" s="44" t="n"/>
       <c r="P112" s="44" t="n"/>
       <c r="Q112" s="44" t="n"/>
+      <c r="R112" s="44" t="n"/>
+      <c r="S112" s="44" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="44" t="n"/>
@@ -6932,6 +6864,8 @@
       <c r="O113" s="44" t="n"/>
       <c r="P113" s="44" t="n"/>
       <c r="Q113" s="44" t="n"/>
+      <c r="R113" s="44" t="n"/>
+      <c r="S113" s="44" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="44" t="n"/>
@@ -6951,6 +6885,8 @@
       <c r="O114" s="44" t="n"/>
       <c r="P114" s="44" t="n"/>
       <c r="Q114" s="44" t="n"/>
+      <c r="R114" s="44" t="n"/>
+      <c r="S114" s="44" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="44" t="n"/>
@@ -6970,6 +6906,8 @@
       <c r="O115" s="44" t="n"/>
       <c r="P115" s="44" t="n"/>
       <c r="Q115" s="44" t="n"/>
+      <c r="R115" s="44" t="n"/>
+      <c r="S115" s="44" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="44" t="n"/>
@@ -6989,6 +6927,8 @@
       <c r="O116" s="44" t="n"/>
       <c r="P116" s="44" t="n"/>
       <c r="Q116" s="44" t="n"/>
+      <c r="R116" s="44" t="n"/>
+      <c r="S116" s="44" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="44" t="n"/>
@@ -7008,6 +6948,8 @@
       <c r="O117" s="44" t="n"/>
       <c r="P117" s="44" t="n"/>
       <c r="Q117" s="44" t="n"/>
+      <c r="R117" s="44" t="n"/>
+      <c r="S117" s="44" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="44" t="n"/>
@@ -7027,6 +6969,8 @@
       <c r="O118" s="44" t="n"/>
       <c r="P118" s="44" t="n"/>
       <c r="Q118" s="44" t="n"/>
+      <c r="R118" s="44" t="n"/>
+      <c r="S118" s="44" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="44" t="n"/>
@@ -7046,6 +6990,8 @@
       <c r="O119" s="44" t="n"/>
       <c r="P119" s="44" t="n"/>
       <c r="Q119" s="44" t="n"/>
+      <c r="R119" s="44" t="n"/>
+      <c r="S119" s="44" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="44" t="n"/>
@@ -7065,6 +7011,8 @@
       <c r="O120" s="44" t="n"/>
       <c r="P120" s="44" t="n"/>
       <c r="Q120" s="44" t="n"/>
+      <c r="R120" s="44" t="n"/>
+      <c r="S120" s="44" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="44" t="n"/>
@@ -7084,6 +7032,8 @@
       <c r="O121" s="44" t="n"/>
       <c r="P121" s="44" t="n"/>
       <c r="Q121" s="44" t="n"/>
+      <c r="R121" s="44" t="n"/>
+      <c r="S121" s="44" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="44" t="n"/>
@@ -7103,6 +7053,8 @@
       <c r="O122" s="44" t="n"/>
       <c r="P122" s="44" t="n"/>
       <c r="Q122" s="44" t="n"/>
+      <c r="R122" s="44" t="n"/>
+      <c r="S122" s="44" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="44" t="n"/>
@@ -7122,6 +7074,8 @@
       <c r="O123" s="44" t="n"/>
       <c r="P123" s="44" t="n"/>
       <c r="Q123" s="44" t="n"/>
+      <c r="R123" s="44" t="n"/>
+      <c r="S123" s="44" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="44" t="n"/>
@@ -7141,6 +7095,8 @@
       <c r="O124" s="44" t="n"/>
       <c r="P124" s="44" t="n"/>
       <c r="Q124" s="44" t="n"/>
+      <c r="R124" s="44" t="n"/>
+      <c r="S124" s="44" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="44" t="n"/>
@@ -7160,6 +7116,8 @@
       <c r="O125" s="44" t="n"/>
       <c r="P125" s="44" t="n"/>
       <c r="Q125" s="44" t="n"/>
+      <c r="R125" s="44" t="n"/>
+      <c r="S125" s="44" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="44" t="n"/>
@@ -7179,6 +7137,8 @@
       <c r="O126" s="44" t="n"/>
       <c r="P126" s="44" t="n"/>
       <c r="Q126" s="44" t="n"/>
+      <c r="R126" s="44" t="n"/>
+      <c r="S126" s="44" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="44" t="n"/>
@@ -7198,6 +7158,8 @@
       <c r="O127" s="44" t="n"/>
       <c r="P127" s="44" t="n"/>
       <c r="Q127" s="44" t="n"/>
+      <c r="R127" s="44" t="n"/>
+      <c r="S127" s="44" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="44" t="n"/>
@@ -7217,6 +7179,8 @@
       <c r="O128" s="44" t="n"/>
       <c r="P128" s="44" t="n"/>
       <c r="Q128" s="44" t="n"/>
+      <c r="R128" s="44" t="n"/>
+      <c r="S128" s="44" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="44" t="n"/>
@@ -7236,6 +7200,8 @@
       <c r="O129" s="44" t="n"/>
       <c r="P129" s="44" t="n"/>
       <c r="Q129" s="44" t="n"/>
+      <c r="R129" s="44" t="n"/>
+      <c r="S129" s="44" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="44" t="n"/>
@@ -7255,6 +7221,8 @@
       <c r="O130" s="44" t="n"/>
       <c r="P130" s="44" t="n"/>
       <c r="Q130" s="44" t="n"/>
+      <c r="R130" s="44" t="n"/>
+      <c r="S130" s="44" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="44" t="n"/>
@@ -7274,6 +7242,8 @@
       <c r="O131" s="44" t="n"/>
       <c r="P131" s="44" t="n"/>
       <c r="Q131" s="44" t="n"/>
+      <c r="R131" s="44" t="n"/>
+      <c r="S131" s="44" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="44" t="n"/>
@@ -7293,6 +7263,8 @@
       <c r="O132" s="44" t="n"/>
       <c r="P132" s="44" t="n"/>
       <c r="Q132" s="44" t="n"/>
+      <c r="R132" s="44" t="n"/>
+      <c r="S132" s="44" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="44" t="n"/>
@@ -7312,6 +7284,8 @@
       <c r="O133" s="44" t="n"/>
       <c r="P133" s="44" t="n"/>
       <c r="Q133" s="44" t="n"/>
+      <c r="R133" s="44" t="n"/>
+      <c r="S133" s="44" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="44" t="n"/>
@@ -7331,6 +7305,8 @@
       <c r="O134" s="44" t="n"/>
       <c r="P134" s="44" t="n"/>
       <c r="Q134" s="44" t="n"/>
+      <c r="R134" s="44" t="n"/>
+      <c r="S134" s="44" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="44" t="n"/>
@@ -7350,6 +7326,8 @@
       <c r="O135" s="44" t="n"/>
       <c r="P135" s="44" t="n"/>
       <c r="Q135" s="44" t="n"/>
+      <c r="R135" s="44" t="n"/>
+      <c r="S135" s="44" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="44" t="n"/>
@@ -7369,6 +7347,8 @@
       <c r="O136" s="44" t="n"/>
       <c r="P136" s="44" t="n"/>
       <c r="Q136" s="44" t="n"/>
+      <c r="R136" s="44" t="n"/>
+      <c r="S136" s="44" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="44" t="n"/>
@@ -7388,6 +7368,8 @@
       <c r="O137" s="44" t="n"/>
       <c r="P137" s="44" t="n"/>
       <c r="Q137" s="44" t="n"/>
+      <c r="R137" s="44" t="n"/>
+      <c r="S137" s="44" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="44" t="n"/>
@@ -7407,6 +7389,8 @@
       <c r="O138" s="44" t="n"/>
       <c r="P138" s="44" t="n"/>
       <c r="Q138" s="44" t="n"/>
+      <c r="R138" s="44" t="n"/>
+      <c r="S138" s="44" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="44" t="n"/>
@@ -7426,6 +7410,8 @@
       <c r="O139" s="44" t="n"/>
       <c r="P139" s="44" t="n"/>
       <c r="Q139" s="44" t="n"/>
+      <c r="R139" s="44" t="n"/>
+      <c r="S139" s="44" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="44" t="n"/>
@@ -7445,6 +7431,8 @@
       <c r="O140" s="44" t="n"/>
       <c r="P140" s="44" t="n"/>
       <c r="Q140" s="44" t="n"/>
+      <c r="R140" s="44" t="n"/>
+      <c r="S140" s="44" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="44" t="n"/>
@@ -7464,6 +7452,8 @@
       <c r="O141" s="44" t="n"/>
       <c r="P141" s="44" t="n"/>
       <c r="Q141" s="44" t="n"/>
+      <c r="R141" s="44" t="n"/>
+      <c r="S141" s="44" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="44" t="n"/>
@@ -7483,6 +7473,8 @@
       <c r="O142" s="44" t="n"/>
       <c r="P142" s="44" t="n"/>
       <c r="Q142" s="44" t="n"/>
+      <c r="R142" s="44" t="n"/>
+      <c r="S142" s="44" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="44" t="n"/>
@@ -7502,6 +7494,8 @@
       <c r="O143" s="44" t="n"/>
       <c r="P143" s="44" t="n"/>
       <c r="Q143" s="44" t="n"/>
+      <c r="R143" s="44" t="n"/>
+      <c r="S143" s="44" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="44" t="n"/>
@@ -7521,6 +7515,8 @@
       <c r="O144" s="44" t="n"/>
       <c r="P144" s="44" t="n"/>
       <c r="Q144" s="44" t="n"/>
+      <c r="R144" s="44" t="n"/>
+      <c r="S144" s="44" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="44" t="n"/>
@@ -7540,6 +7536,8 @@
       <c r="O145" s="44" t="n"/>
       <c r="P145" s="44" t="n"/>
       <c r="Q145" s="44" t="n"/>
+      <c r="R145" s="44" t="n"/>
+      <c r="S145" s="44" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="44" t="n"/>
@@ -7559,6 +7557,8 @@
       <c r="O146" s="44" t="n"/>
       <c r="P146" s="44" t="n"/>
       <c r="Q146" s="44" t="n"/>
+      <c r="R146" s="44" t="n"/>
+      <c r="S146" s="44" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="44" t="n"/>
@@ -7578,6 +7578,8 @@
       <c r="O147" s="44" t="n"/>
       <c r="P147" s="44" t="n"/>
       <c r="Q147" s="44" t="n"/>
+      <c r="R147" s="44" t="n"/>
+      <c r="S147" s="44" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="44" t="n"/>
@@ -7597,6 +7599,8 @@
       <c r="O148" s="44" t="n"/>
       <c r="P148" s="44" t="n"/>
       <c r="Q148" s="44" t="n"/>
+      <c r="R148" s="44" t="n"/>
+      <c r="S148" s="44" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="44" t="n"/>
@@ -7616,6 +7620,8 @@
       <c r="O149" s="44" t="n"/>
       <c r="P149" s="44" t="n"/>
       <c r="Q149" s="44" t="n"/>
+      <c r="R149" s="44" t="n"/>
+      <c r="S149" s="44" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="44" t="n"/>
@@ -7635,6 +7641,8 @@
       <c r="O150" s="44" t="n"/>
       <c r="P150" s="44" t="n"/>
       <c r="Q150" s="44" t="n"/>
+      <c r="R150" s="44" t="n"/>
+      <c r="S150" s="44" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="44" t="n"/>
@@ -7654,6 +7662,8 @@
       <c r="O151" s="44" t="n"/>
       <c r="P151" s="44" t="n"/>
       <c r="Q151" s="44" t="n"/>
+      <c r="R151" s="44" t="n"/>
+      <c r="S151" s="44" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="44" t="n"/>
@@ -7673,6 +7683,8 @@
       <c r="O152" s="44" t="n"/>
       <c r="P152" s="44" t="n"/>
       <c r="Q152" s="44" t="n"/>
+      <c r="R152" s="44" t="n"/>
+      <c r="S152" s="44" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="44" t="n"/>
@@ -7692,6 +7704,8 @@
       <c r="O153" s="44" t="n"/>
       <c r="P153" s="44" t="n"/>
       <c r="Q153" s="44" t="n"/>
+      <c r="R153" s="44" t="n"/>
+      <c r="S153" s="44" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="44" t="n"/>
@@ -7711,6 +7725,8 @@
       <c r="O154" s="44" t="n"/>
       <c r="P154" s="44" t="n"/>
       <c r="Q154" s="44" t="n"/>
+      <c r="R154" s="44" t="n"/>
+      <c r="S154" s="44" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="44" t="n"/>
@@ -7730,6 +7746,8 @@
       <c r="O155" s="44" t="n"/>
       <c r="P155" s="44" t="n"/>
       <c r="Q155" s="44" t="n"/>
+      <c r="R155" s="44" t="n"/>
+      <c r="S155" s="44" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="44" t="n"/>
@@ -7749,6 +7767,8 @@
       <c r="O156" s="44" t="n"/>
       <c r="P156" s="44" t="n"/>
       <c r="Q156" s="44" t="n"/>
+      <c r="R156" s="44" t="n"/>
+      <c r="S156" s="44" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="44" t="n"/>
@@ -7768,6 +7788,8 @@
       <c r="O157" s="44" t="n"/>
       <c r="P157" s="44" t="n"/>
       <c r="Q157" s="44" t="n"/>
+      <c r="R157" s="44" t="n"/>
+      <c r="S157" s="44" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="44" t="n"/>
@@ -7787,6 +7809,8 @@
       <c r="O158" s="44" t="n"/>
       <c r="P158" s="44" t="n"/>
       <c r="Q158" s="44" t="n"/>
+      <c r="R158" s="44" t="n"/>
+      <c r="S158" s="44" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="44" t="n"/>
@@ -7806,6 +7830,8 @@
       <c r="O159" s="44" t="n"/>
       <c r="P159" s="44" t="n"/>
       <c r="Q159" s="44" t="n"/>
+      <c r="R159" s="44" t="n"/>
+      <c r="S159" s="44" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="44" t="n"/>
@@ -7825,6 +7851,8 @@
       <c r="O160" s="44" t="n"/>
       <c r="P160" s="44" t="n"/>
       <c r="Q160" s="44" t="n"/>
+      <c r="R160" s="44" t="n"/>
+      <c r="S160" s="44" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="44" t="n"/>
@@ -7844,6 +7872,8 @@
       <c r="O161" s="44" t="n"/>
       <c r="P161" s="44" t="n"/>
       <c r="Q161" s="44" t="n"/>
+      <c r="R161" s="44" t="n"/>
+      <c r="S161" s="44" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="44" t="n"/>
@@ -7863,6 +7893,8 @@
       <c r="O162" s="44" t="n"/>
       <c r="P162" s="44" t="n"/>
       <c r="Q162" s="44" t="n"/>
+      <c r="R162" s="44" t="n"/>
+      <c r="S162" s="44" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="44" t="n"/>
@@ -7882,6 +7914,8 @@
       <c r="O163" s="44" t="n"/>
       <c r="P163" s="44" t="n"/>
       <c r="Q163" s="44" t="n"/>
+      <c r="R163" s="44" t="n"/>
+      <c r="S163" s="44" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="44" t="n"/>
@@ -7901,6 +7935,8 @@
       <c r="O164" s="44" t="n"/>
       <c r="P164" s="44" t="n"/>
       <c r="Q164" s="44" t="n"/>
+      <c r="R164" s="44" t="n"/>
+      <c r="S164" s="44" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="44" t="n"/>
@@ -7920,6 +7956,8 @@
       <c r="O165" s="44" t="n"/>
       <c r="P165" s="44" t="n"/>
       <c r="Q165" s="44" t="n"/>
+      <c r="R165" s="44" t="n"/>
+      <c r="S165" s="44" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="44" t="n"/>
@@ -7939,6 +7977,8 @@
       <c r="O166" s="44" t="n"/>
       <c r="P166" s="44" t="n"/>
       <c r="Q166" s="44" t="n"/>
+      <c r="R166" s="44" t="n"/>
+      <c r="S166" s="44" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="44" t="n"/>
@@ -7958,6 +7998,8 @@
       <c r="O167" s="44" t="n"/>
       <c r="P167" s="44" t="n"/>
       <c r="Q167" s="44" t="n"/>
+      <c r="R167" s="44" t="n"/>
+      <c r="S167" s="44" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="44" t="n"/>
@@ -7977,6 +8019,8 @@
       <c r="O168" s="44" t="n"/>
       <c r="P168" s="44" t="n"/>
       <c r="Q168" s="44" t="n"/>
+      <c r="R168" s="44" t="n"/>
+      <c r="S168" s="44" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="44" t="n"/>
@@ -7996,6 +8040,8 @@
       <c r="O169" s="44" t="n"/>
       <c r="P169" s="44" t="n"/>
       <c r="Q169" s="44" t="n"/>
+      <c r="R169" s="44" t="n"/>
+      <c r="S169" s="44" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="44" t="n"/>
@@ -8015,6 +8061,8 @@
       <c r="O170" s="44" t="n"/>
       <c r="P170" s="44" t="n"/>
       <c r="Q170" s="44" t="n"/>
+      <c r="R170" s="44" t="n"/>
+      <c r="S170" s="44" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="44" t="n"/>
@@ -8034,6 +8082,8 @@
       <c r="O171" s="44" t="n"/>
       <c r="P171" s="44" t="n"/>
       <c r="Q171" s="44" t="n"/>
+      <c r="R171" s="44" t="n"/>
+      <c r="S171" s="44" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="44" t="n"/>
@@ -8053,6 +8103,8 @@
       <c r="O172" s="44" t="n"/>
       <c r="P172" s="44" t="n"/>
       <c r="Q172" s="44" t="n"/>
+      <c r="R172" s="44" t="n"/>
+      <c r="S172" s="44" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="44" t="n"/>
@@ -8072,6 +8124,8 @@
       <c r="O173" s="44" t="n"/>
       <c r="P173" s="44" t="n"/>
       <c r="Q173" s="44" t="n"/>
+      <c r="R173" s="44" t="n"/>
+      <c r="S173" s="44" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="44" t="n"/>
@@ -8091,6 +8145,8 @@
       <c r="O174" s="44" t="n"/>
       <c r="P174" s="44" t="n"/>
       <c r="Q174" s="44" t="n"/>
+      <c r="R174" s="44" t="n"/>
+      <c r="S174" s="44" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="44" t="n"/>
@@ -8110,6 +8166,8 @@
       <c r="O175" s="44" t="n"/>
       <c r="P175" s="44" t="n"/>
       <c r="Q175" s="44" t="n"/>
+      <c r="R175" s="44" t="n"/>
+      <c r="S175" s="44" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="44" t="n"/>
@@ -8129,6 +8187,8 @@
       <c r="O176" s="44" t="n"/>
       <c r="P176" s="44" t="n"/>
       <c r="Q176" s="44" t="n"/>
+      <c r="R176" s="44" t="n"/>
+      <c r="S176" s="44" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="44" t="n"/>
@@ -8148,6 +8208,8 @@
       <c r="O177" s="44" t="n"/>
       <c r="P177" s="44" t="n"/>
       <c r="Q177" s="44" t="n"/>
+      <c r="R177" s="44" t="n"/>
+      <c r="S177" s="44" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="44" t="n"/>
@@ -8167,6 +8229,8 @@
       <c r="O178" s="44" t="n"/>
       <c r="P178" s="44" t="n"/>
       <c r="Q178" s="44" t="n"/>
+      <c r="R178" s="44" t="n"/>
+      <c r="S178" s="44" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="44" t="n"/>
@@ -8186,6 +8250,8 @@
       <c r="O179" s="44" t="n"/>
       <c r="P179" s="44" t="n"/>
       <c r="Q179" s="44" t="n"/>
+      <c r="R179" s="44" t="n"/>
+      <c r="S179" s="44" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="44" t="n"/>
@@ -8205,6 +8271,8 @@
       <c r="O180" s="44" t="n"/>
       <c r="P180" s="44" t="n"/>
       <c r="Q180" s="44" t="n"/>
+      <c r="R180" s="44" t="n"/>
+      <c r="S180" s="44" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="44" t="n"/>
@@ -8224,6 +8292,8 @@
       <c r="O181" s="44" t="n"/>
       <c r="P181" s="44" t="n"/>
       <c r="Q181" s="44" t="n"/>
+      <c r="R181" s="44" t="n"/>
+      <c r="S181" s="44" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="44" t="n"/>
@@ -8243,6 +8313,8 @@
       <c r="O182" s="44" t="n"/>
       <c r="P182" s="44" t="n"/>
       <c r="Q182" s="44" t="n"/>
+      <c r="R182" s="44" t="n"/>
+      <c r="S182" s="44" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="44" t="n"/>
@@ -8262,6 +8334,8 @@
       <c r="O183" s="44" t="n"/>
       <c r="P183" s="44" t="n"/>
       <c r="Q183" s="44" t="n"/>
+      <c r="R183" s="44" t="n"/>
+      <c r="S183" s="44" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="44" t="n"/>
@@ -8281,6 +8355,8 @@
       <c r="O184" s="44" t="n"/>
       <c r="P184" s="44" t="n"/>
       <c r="Q184" s="44" t="n"/>
+      <c r="R184" s="44" t="n"/>
+      <c r="S184" s="44" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="44" t="n"/>
@@ -8300,6 +8376,8 @@
       <c r="O185" s="44" t="n"/>
       <c r="P185" s="44" t="n"/>
       <c r="Q185" s="44" t="n"/>
+      <c r="R185" s="44" t="n"/>
+      <c r="S185" s="44" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="44" t="n"/>
@@ -8319,6 +8397,8 @@
       <c r="O186" s="44" t="n"/>
       <c r="P186" s="44" t="n"/>
       <c r="Q186" s="44" t="n"/>
+      <c r="R186" s="44" t="n"/>
+      <c r="S186" s="44" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="44" t="n"/>
@@ -8338,6 +8418,8 @@
       <c r="O187" s="44" t="n"/>
       <c r="P187" s="44" t="n"/>
       <c r="Q187" s="44" t="n"/>
+      <c r="R187" s="44" t="n"/>
+      <c r="S187" s="44" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="44" t="n"/>
@@ -8357,6 +8439,8 @@
       <c r="O188" s="44" t="n"/>
       <c r="P188" s="44" t="n"/>
       <c r="Q188" s="44" t="n"/>
+      <c r="R188" s="44" t="n"/>
+      <c r="S188" s="44" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="44" t="n"/>
@@ -8376,6 +8460,8 @@
       <c r="O189" s="44" t="n"/>
       <c r="P189" s="44" t="n"/>
       <c r="Q189" s="44" t="n"/>
+      <c r="R189" s="44" t="n"/>
+      <c r="S189" s="44" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="44" t="n"/>
@@ -8395,6 +8481,8 @@
       <c r="O190" s="44" t="n"/>
       <c r="P190" s="44" t="n"/>
       <c r="Q190" s="44" t="n"/>
+      <c r="R190" s="44" t="n"/>
+      <c r="S190" s="44" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="44" t="n"/>
@@ -8414,6 +8502,8 @@
       <c r="O191" s="44" t="n"/>
       <c r="P191" s="44" t="n"/>
       <c r="Q191" s="44" t="n"/>
+      <c r="R191" s="44" t="n"/>
+      <c r="S191" s="44" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="44" t="n"/>
@@ -8433,6 +8523,8 @@
       <c r="O192" s="44" t="n"/>
       <c r="P192" s="44" t="n"/>
       <c r="Q192" s="44" t="n"/>
+      <c r="R192" s="44" t="n"/>
+      <c r="S192" s="44" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="44" t="n"/>
@@ -8452,6 +8544,8 @@
       <c r="O193" s="44" t="n"/>
       <c r="P193" s="44" t="n"/>
       <c r="Q193" s="44" t="n"/>
+      <c r="R193" s="44" t="n"/>
+      <c r="S193" s="44" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="44" t="n"/>
@@ -8471,6 +8565,8 @@
       <c r="O194" s="44" t="n"/>
       <c r="P194" s="44" t="n"/>
       <c r="Q194" s="44" t="n"/>
+      <c r="R194" s="44" t="n"/>
+      <c r="S194" s="44" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="44" t="n"/>
@@ -8490,6 +8586,8 @@
       <c r="O195" s="44" t="n"/>
       <c r="P195" s="44" t="n"/>
       <c r="Q195" s="44" t="n"/>
+      <c r="R195" s="44" t="n"/>
+      <c r="S195" s="44" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="44" t="n"/>
@@ -8509,6 +8607,8 @@
       <c r="O196" s="44" t="n"/>
       <c r="P196" s="44" t="n"/>
       <c r="Q196" s="44" t="n"/>
+      <c r="R196" s="44" t="n"/>
+      <c r="S196" s="44" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="44" t="n"/>
@@ -8528,6 +8628,8 @@
       <c r="O197" s="44" t="n"/>
       <c r="P197" s="44" t="n"/>
       <c r="Q197" s="44" t="n"/>
+      <c r="R197" s="44" t="n"/>
+      <c r="S197" s="44" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="44" t="n"/>
@@ -8547,6 +8649,8 @@
       <c r="O198" s="44" t="n"/>
       <c r="P198" s="44" t="n"/>
       <c r="Q198" s="44" t="n"/>
+      <c r="R198" s="44" t="n"/>
+      <c r="S198" s="44" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="44" t="n"/>
@@ -8566,6 +8670,8 @@
       <c r="O199" s="44" t="n"/>
       <c r="P199" s="44" t="n"/>
       <c r="Q199" s="44" t="n"/>
+      <c r="R199" s="44" t="n"/>
+      <c r="S199" s="44" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="44" t="n"/>
@@ -8585,6 +8691,8 @@
       <c r="O200" s="44" t="n"/>
       <c r="P200" s="44" t="n"/>
       <c r="Q200" s="44" t="n"/>
+      <c r="R200" s="44" t="n"/>
+      <c r="S200" s="44" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="44" t="n"/>
@@ -8604,6 +8712,8 @@
       <c r="O201" s="44" t="n"/>
       <c r="P201" s="44" t="n"/>
       <c r="Q201" s="44" t="n"/>
+      <c r="R201" s="44" t="n"/>
+      <c r="S201" s="44" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="44" t="n"/>
@@ -8623,6 +8733,8 @@
       <c r="O202" s="44" t="n"/>
       <c r="P202" s="44" t="n"/>
       <c r="Q202" s="44" t="n"/>
+      <c r="R202" s="44" t="n"/>
+      <c r="S202" s="44" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="44" t="n"/>
@@ -8642,6 +8754,8 @@
       <c r="O203" s="44" t="n"/>
       <c r="P203" s="44" t="n"/>
       <c r="Q203" s="44" t="n"/>
+      <c r="R203" s="44" t="n"/>
+      <c r="S203" s="44" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="44" t="n"/>
@@ -8661,6 +8775,8 @@
       <c r="O204" s="44" t="n"/>
       <c r="P204" s="44" t="n"/>
       <c r="Q204" s="44" t="n"/>
+      <c r="R204" s="44" t="n"/>
+      <c r="S204" s="44" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="44" t="n"/>
@@ -8680,6 +8796,8 @@
       <c r="O205" s="44" t="n"/>
       <c r="P205" s="44" t="n"/>
       <c r="Q205" s="44" t="n"/>
+      <c r="R205" s="44" t="n"/>
+      <c r="S205" s="44" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="44" t="n"/>
@@ -8699,6 +8817,8 @@
       <c r="O206" s="44" t="n"/>
       <c r="P206" s="44" t="n"/>
       <c r="Q206" s="44" t="n"/>
+      <c r="R206" s="44" t="n"/>
+      <c r="S206" s="44" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="44" t="n"/>
@@ -8718,6 +8838,8 @@
       <c r="O207" s="44" t="n"/>
       <c r="P207" s="44" t="n"/>
       <c r="Q207" s="44" t="n"/>
+      <c r="R207" s="44" t="n"/>
+      <c r="S207" s="44" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="44" t="n"/>
@@ -8737,6 +8859,8 @@
       <c r="O208" s="44" t="n"/>
       <c r="P208" s="44" t="n"/>
       <c r="Q208" s="44" t="n"/>
+      <c r="R208" s="44" t="n"/>
+      <c r="S208" s="44" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="44" t="n"/>
@@ -8756,6 +8880,8 @@
       <c r="O209" s="44" t="n"/>
       <c r="P209" s="44" t="n"/>
       <c r="Q209" s="44" t="n"/>
+      <c r="R209" s="44" t="n"/>
+      <c r="S209" s="44" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="44" t="n"/>
@@ -8775,6 +8901,8 @@
       <c r="O210" s="44" t="n"/>
       <c r="P210" s="44" t="n"/>
       <c r="Q210" s="44" t="n"/>
+      <c r="R210" s="44" t="n"/>
+      <c r="S210" s="44" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="44" t="n"/>
@@ -8794,6 +8922,8 @@
       <c r="O211" s="44" t="n"/>
       <c r="P211" s="44" t="n"/>
       <c r="Q211" s="44" t="n"/>
+      <c r="R211" s="44" t="n"/>
+      <c r="S211" s="44" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="44" t="n"/>
@@ -8813,6 +8943,8 @@
       <c r="O212" s="44" t="n"/>
       <c r="P212" s="44" t="n"/>
       <c r="Q212" s="44" t="n"/>
+      <c r="R212" s="44" t="n"/>
+      <c r="S212" s="44" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="44" t="n"/>
@@ -8832,6 +8964,8 @@
       <c r="O213" s="44" t="n"/>
       <c r="P213" s="44" t="n"/>
       <c r="Q213" s="44" t="n"/>
+      <c r="R213" s="44" t="n"/>
+      <c r="S213" s="44" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="44" t="n"/>
@@ -8851,6 +8985,8 @@
       <c r="O214" s="44" t="n"/>
       <c r="P214" s="44" t="n"/>
       <c r="Q214" s="44" t="n"/>
+      <c r="R214" s="44" t="n"/>
+      <c r="S214" s="44" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="44" t="n"/>
@@ -8870,6 +9006,8 @@
       <c r="O215" s="44" t="n"/>
       <c r="P215" s="44" t="n"/>
       <c r="Q215" s="44" t="n"/>
+      <c r="R215" s="44" t="n"/>
+      <c r="S215" s="44" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="44" t="n"/>
@@ -8889,6 +9027,8 @@
       <c r="O216" s="44" t="n"/>
       <c r="P216" s="44" t="n"/>
       <c r="Q216" s="44" t="n"/>
+      <c r="R216" s="44" t="n"/>
+      <c r="S216" s="44" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="44" t="n"/>
@@ -8908,6 +9048,8 @@
       <c r="O217" s="44" t="n"/>
       <c r="P217" s="44" t="n"/>
       <c r="Q217" s="44" t="n"/>
+      <c r="R217" s="44" t="n"/>
+      <c r="S217" s="44" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="44" t="n"/>
@@ -8927,6 +9069,8 @@
       <c r="O218" s="44" t="n"/>
       <c r="P218" s="44" t="n"/>
       <c r="Q218" s="44" t="n"/>
+      <c r="R218" s="44" t="n"/>
+      <c r="S218" s="44" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="44" t="n"/>
@@ -8946,6 +9090,8 @@
       <c r="O219" s="44" t="n"/>
       <c r="P219" s="44" t="n"/>
       <c r="Q219" s="44" t="n"/>
+      <c r="R219" s="44" t="n"/>
+      <c r="S219" s="44" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="44" t="n"/>
@@ -8965,6 +9111,8 @@
       <c r="O220" s="44" t="n"/>
       <c r="P220" s="44" t="n"/>
       <c r="Q220" s="44" t="n"/>
+      <c r="R220" s="44" t="n"/>
+      <c r="S220" s="44" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="44" t="n"/>
@@ -8984,6 +9132,8 @@
       <c r="O221" s="44" t="n"/>
       <c r="P221" s="44" t="n"/>
       <c r="Q221" s="44" t="n"/>
+      <c r="R221" s="44" t="n"/>
+      <c r="S221" s="44" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="44" t="n"/>
@@ -9003,6 +9153,8 @@
       <c r="O222" s="44" t="n"/>
       <c r="P222" s="44" t="n"/>
       <c r="Q222" s="44" t="n"/>
+      <c r="R222" s="44" t="n"/>
+      <c r="S222" s="44" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="44" t="n"/>
@@ -9022,6 +9174,8 @@
       <c r="O223" s="44" t="n"/>
       <c r="P223" s="44" t="n"/>
       <c r="Q223" s="44" t="n"/>
+      <c r="R223" s="44" t="n"/>
+      <c r="S223" s="44" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="44" t="n"/>
@@ -9041,6 +9195,8 @@
       <c r="O224" s="44" t="n"/>
       <c r="P224" s="44" t="n"/>
       <c r="Q224" s="44" t="n"/>
+      <c r="R224" s="44" t="n"/>
+      <c r="S224" s="44" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="44" t="n"/>
@@ -9060,6 +9216,8 @@
       <c r="O225" s="44" t="n"/>
       <c r="P225" s="44" t="n"/>
       <c r="Q225" s="44" t="n"/>
+      <c r="R225" s="44" t="n"/>
+      <c r="S225" s="44" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="44" t="n"/>
@@ -9079,6 +9237,8 @@
       <c r="O226" s="44" t="n"/>
       <c r="P226" s="44" t="n"/>
       <c r="Q226" s="44" t="n"/>
+      <c r="R226" s="44" t="n"/>
+      <c r="S226" s="44" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="44" t="n"/>
@@ -9098,6 +9258,8 @@
       <c r="O227" s="44" t="n"/>
       <c r="P227" s="44" t="n"/>
       <c r="Q227" s="44" t="n"/>
+      <c r="R227" s="44" t="n"/>
+      <c r="S227" s="44" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="44" t="n"/>
@@ -9117,6 +9279,8 @@
       <c r="O228" s="44" t="n"/>
       <c r="P228" s="44" t="n"/>
       <c r="Q228" s="44" t="n"/>
+      <c r="R228" s="44" t="n"/>
+      <c r="S228" s="44" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="44" t="n"/>
@@ -9136,6 +9300,8 @@
       <c r="O229" s="44" t="n"/>
       <c r="P229" s="44" t="n"/>
       <c r="Q229" s="44" t="n"/>
+      <c r="R229" s="44" t="n"/>
+      <c r="S229" s="44" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="44" t="n"/>
@@ -9155,6 +9321,8 @@
       <c r="O230" s="44" t="n"/>
       <c r="P230" s="44" t="n"/>
       <c r="Q230" s="44" t="n"/>
+      <c r="R230" s="44" t="n"/>
+      <c r="S230" s="44" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="44" t="n"/>
@@ -9174,6 +9342,8 @@
       <c r="O231" s="44" t="n"/>
       <c r="P231" s="44" t="n"/>
       <c r="Q231" s="44" t="n"/>
+      <c r="R231" s="44" t="n"/>
+      <c r="S231" s="44" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="44" t="n"/>
@@ -9193,6 +9363,8 @@
       <c r="O232" s="44" t="n"/>
       <c r="P232" s="44" t="n"/>
       <c r="Q232" s="44" t="n"/>
+      <c r="R232" s="44" t="n"/>
+      <c r="S232" s="44" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="44" t="n"/>
@@ -9212,6 +9384,8 @@
       <c r="O233" s="44" t="n"/>
       <c r="P233" s="44" t="n"/>
       <c r="Q233" s="44" t="n"/>
+      <c r="R233" s="44" t="n"/>
+      <c r="S233" s="44" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="44" t="n"/>
@@ -9231,6 +9405,8 @@
       <c r="O234" s="44" t="n"/>
       <c r="P234" s="44" t="n"/>
       <c r="Q234" s="44" t="n"/>
+      <c r="R234" s="44" t="n"/>
+      <c r="S234" s="44" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="44" t="n"/>
@@ -9250,6 +9426,8 @@
       <c r="O235" s="44" t="n"/>
       <c r="P235" s="44" t="n"/>
       <c r="Q235" s="44" t="n"/>
+      <c r="R235" s="44" t="n"/>
+      <c r="S235" s="44" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="44" t="n"/>
@@ -9269,6 +9447,8 @@
       <c r="O236" s="44" t="n"/>
       <c r="P236" s="44" t="n"/>
       <c r="Q236" s="44" t="n"/>
+      <c r="R236" s="44" t="n"/>
+      <c r="S236" s="44" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="44" t="n"/>
@@ -9288,6 +9468,8 @@
       <c r="O237" s="44" t="n"/>
       <c r="P237" s="44" t="n"/>
       <c r="Q237" s="44" t="n"/>
+      <c r="R237" s="44" t="n"/>
+      <c r="S237" s="44" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="44" t="n"/>
@@ -9307,6 +9489,8 @@
       <c r="O238" s="44" t="n"/>
       <c r="P238" s="44" t="n"/>
       <c r="Q238" s="44" t="n"/>
+      <c r="R238" s="44" t="n"/>
+      <c r="S238" s="44" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="44" t="n"/>
@@ -9326,6 +9510,8 @@
       <c r="O239" s="44" t="n"/>
       <c r="P239" s="44" t="n"/>
       <c r="Q239" s="44" t="n"/>
+      <c r="R239" s="44" t="n"/>
+      <c r="S239" s="44" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="44" t="n"/>
@@ -9345,6 +9531,8 @@
       <c r="O240" s="44" t="n"/>
       <c r="P240" s="44" t="n"/>
       <c r="Q240" s="44" t="n"/>
+      <c r="R240" s="44" t="n"/>
+      <c r="S240" s="44" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="44" t="n"/>
@@ -9364,6 +9552,8 @@
       <c r="O241" s="44" t="n"/>
       <c r="P241" s="44" t="n"/>
       <c r="Q241" s="44" t="n"/>
+      <c r="R241" s="44" t="n"/>
+      <c r="S241" s="44" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="44" t="n"/>
@@ -9383,6 +9573,8 @@
       <c r="O242" s="44" t="n"/>
       <c r="P242" s="44" t="n"/>
       <c r="Q242" s="44" t="n"/>
+      <c r="R242" s="44" t="n"/>
+      <c r="S242" s="44" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="44" t="n"/>
@@ -9402,6 +9594,8 @@
       <c r="O243" s="44" t="n"/>
       <c r="P243" s="44" t="n"/>
       <c r="Q243" s="44" t="n"/>
+      <c r="R243" s="44" t="n"/>
+      <c r="S243" s="44" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="44" t="n"/>
@@ -9421,6 +9615,8 @@
       <c r="O244" s="44" t="n"/>
       <c r="P244" s="44" t="n"/>
       <c r="Q244" s="44" t="n"/>
+      <c r="R244" s="44" t="n"/>
+      <c r="S244" s="44" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="44" t="n"/>
@@ -9440,6 +9636,8 @@
       <c r="O245" s="44" t="n"/>
       <c r="P245" s="44" t="n"/>
       <c r="Q245" s="44" t="n"/>
+      <c r="R245" s="44" t="n"/>
+      <c r="S245" s="44" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="44" t="n"/>
@@ -9459,6 +9657,8 @@
       <c r="O246" s="44" t="n"/>
       <c r="P246" s="44" t="n"/>
       <c r="Q246" s="44" t="n"/>
+      <c r="R246" s="44" t="n"/>
+      <c r="S246" s="44" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="44" t="n"/>
@@ -9478,6 +9678,8 @@
       <c r="O247" s="44" t="n"/>
       <c r="P247" s="44" t="n"/>
       <c r="Q247" s="44" t="n"/>
+      <c r="R247" s="44" t="n"/>
+      <c r="S247" s="44" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="44" t="n"/>
@@ -9497,6 +9699,8 @@
       <c r="O248" s="44" t="n"/>
       <c r="P248" s="44" t="n"/>
       <c r="Q248" s="44" t="n"/>
+      <c r="R248" s="44" t="n"/>
+      <c r="S248" s="44" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="44" t="n"/>
@@ -9516,6 +9720,8 @@
       <c r="O249" s="44" t="n"/>
       <c r="P249" s="44" t="n"/>
       <c r="Q249" s="44" t="n"/>
+      <c r="R249" s="44" t="n"/>
+      <c r="S249" s="44" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="44" t="n"/>
@@ -9535,6 +9741,8 @@
       <c r="O250" s="44" t="n"/>
       <c r="P250" s="44" t="n"/>
       <c r="Q250" s="44" t="n"/>
+      <c r="R250" s="44" t="n"/>
+      <c r="S250" s="44" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="44" t="n"/>
@@ -9554,6 +9762,8 @@
       <c r="O251" s="44" t="n"/>
       <c r="P251" s="44" t="n"/>
       <c r="Q251" s="44" t="n"/>
+      <c r="R251" s="44" t="n"/>
+      <c r="S251" s="44" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="44" t="n"/>
@@ -9573,6 +9783,8 @@
       <c r="O252" s="44" t="n"/>
       <c r="P252" s="44" t="n"/>
       <c r="Q252" s="44" t="n"/>
+      <c r="R252" s="44" t="n"/>
+      <c r="S252" s="44" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="44" t="n"/>
@@ -9592,6 +9804,8 @@
       <c r="O253" s="44" t="n"/>
       <c r="P253" s="44" t="n"/>
       <c r="Q253" s="44" t="n"/>
+      <c r="R253" s="44" t="n"/>
+      <c r="S253" s="44" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="44" t="n"/>
@@ -9611,6 +9825,8 @@
       <c r="O254" s="44" t="n"/>
       <c r="P254" s="44" t="n"/>
       <c r="Q254" s="44" t="n"/>
+      <c r="R254" s="44" t="n"/>
+      <c r="S254" s="44" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="44" t="n"/>
@@ -9630,6 +9846,8 @@
       <c r="O255" s="44" t="n"/>
       <c r="P255" s="44" t="n"/>
       <c r="Q255" s="44" t="n"/>
+      <c r="R255" s="44" t="n"/>
+      <c r="S255" s="44" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="44" t="n"/>
@@ -9649,6 +9867,8 @@
       <c r="O256" s="44" t="n"/>
       <c r="P256" s="44" t="n"/>
       <c r="Q256" s="44" t="n"/>
+      <c r="R256" s="44" t="n"/>
+      <c r="S256" s="44" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="44" t="n"/>
@@ -9668,6 +9888,8 @@
       <c r="O257" s="44" t="n"/>
       <c r="P257" s="44" t="n"/>
       <c r="Q257" s="44" t="n"/>
+      <c r="R257" s="44" t="n"/>
+      <c r="S257" s="44" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="44" t="n"/>
@@ -9687,6 +9909,8 @@
       <c r="O258" s="44" t="n"/>
       <c r="P258" s="44" t="n"/>
       <c r="Q258" s="44" t="n"/>
+      <c r="R258" s="44" t="n"/>
+      <c r="S258" s="44" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="44" t="n"/>
@@ -9706,6 +9930,8 @@
       <c r="O259" s="44" t="n"/>
       <c r="P259" s="44" t="n"/>
       <c r="Q259" s="44" t="n"/>
+      <c r="R259" s="44" t="n"/>
+      <c r="S259" s="44" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="44" t="n"/>
@@ -9725,6 +9951,8 @@
       <c r="O260" s="44" t="n"/>
       <c r="P260" s="44" t="n"/>
       <c r="Q260" s="44" t="n"/>
+      <c r="R260" s="44" t="n"/>
+      <c r="S260" s="44" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="44" t="n"/>
@@ -9744,6 +9972,8 @@
       <c r="O261" s="44" t="n"/>
       <c r="P261" s="44" t="n"/>
       <c r="Q261" s="44" t="n"/>
+      <c r="R261" s="44" t="n"/>
+      <c r="S261" s="44" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="44" t="n"/>
@@ -9763,6 +9993,8 @@
       <c r="O262" s="44" t="n"/>
       <c r="P262" s="44" t="n"/>
       <c r="Q262" s="44" t="n"/>
+      <c r="R262" s="44" t="n"/>
+      <c r="S262" s="44" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="44" t="n"/>
@@ -9782,6 +10014,8 @@
       <c r="O263" s="44" t="n"/>
       <c r="P263" s="44" t="n"/>
       <c r="Q263" s="44" t="n"/>
+      <c r="R263" s="44" t="n"/>
+      <c r="S263" s="44" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="44" t="n"/>
@@ -9801,6 +10035,8 @@
       <c r="O264" s="44" t="n"/>
       <c r="P264" s="44" t="n"/>
       <c r="Q264" s="44" t="n"/>
+      <c r="R264" s="44" t="n"/>
+      <c r="S264" s="44" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="44" t="n"/>
@@ -9820,6 +10056,8 @@
       <c r="O265" s="44" t="n"/>
       <c r="P265" s="44" t="n"/>
       <c r="Q265" s="44" t="n"/>
+      <c r="R265" s="44" t="n"/>
+      <c r="S265" s="44" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="44" t="n"/>
@@ -9839,6 +10077,8 @@
       <c r="O266" s="44" t="n"/>
       <c r="P266" s="44" t="n"/>
       <c r="Q266" s="44" t="n"/>
+      <c r="R266" s="44" t="n"/>
+      <c r="S266" s="44" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="44" t="n"/>
@@ -9858,6 +10098,8 @@
       <c r="O267" s="44" t="n"/>
       <c r="P267" s="44" t="n"/>
       <c r="Q267" s="44" t="n"/>
+      <c r="R267" s="44" t="n"/>
+      <c r="S267" s="44" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="44" t="n"/>
@@ -9877,6 +10119,8 @@
       <c r="O268" s="44" t="n"/>
       <c r="P268" s="44" t="n"/>
       <c r="Q268" s="44" t="n"/>
+      <c r="R268" s="44" t="n"/>
+      <c r="S268" s="44" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="44" t="n"/>
@@ -9896,6 +10140,8 @@
       <c r="O269" s="44" t="n"/>
       <c r="P269" s="44" t="n"/>
       <c r="Q269" s="44" t="n"/>
+      <c r="R269" s="44" t="n"/>
+      <c r="S269" s="44" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="44" t="n"/>
@@ -9915,6 +10161,8 @@
       <c r="O270" s="44" t="n"/>
       <c r="P270" s="44" t="n"/>
       <c r="Q270" s="44" t="n"/>
+      <c r="R270" s="44" t="n"/>
+      <c r="S270" s="44" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="44" t="n"/>
@@ -9934,6 +10182,8 @@
       <c r="O271" s="44" t="n"/>
       <c r="P271" s="44" t="n"/>
       <c r="Q271" s="44" t="n"/>
+      <c r="R271" s="44" t="n"/>
+      <c r="S271" s="44" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="44" t="n"/>
@@ -9953,6 +10203,8 @@
       <c r="O272" s="44" t="n"/>
       <c r="P272" s="44" t="n"/>
       <c r="Q272" s="44" t="n"/>
+      <c r="R272" s="44" t="n"/>
+      <c r="S272" s="44" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="44" t="n"/>
@@ -9972,6 +10224,8 @@
       <c r="O273" s="44" t="n"/>
       <c r="P273" s="44" t="n"/>
       <c r="Q273" s="44" t="n"/>
+      <c r="R273" s="44" t="n"/>
+      <c r="S273" s="44" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="44" t="n"/>
@@ -9991,6 +10245,8 @@
       <c r="O274" s="44" t="n"/>
       <c r="P274" s="44" t="n"/>
       <c r="Q274" s="44" t="n"/>
+      <c r="R274" s="44" t="n"/>
+      <c r="S274" s="44" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="44" t="n"/>
@@ -10010,6 +10266,8 @@
       <c r="O275" s="44" t="n"/>
       <c r="P275" s="44" t="n"/>
       <c r="Q275" s="44" t="n"/>
+      <c r="R275" s="44" t="n"/>
+      <c r="S275" s="44" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="44" t="n"/>
@@ -10029,6 +10287,8 @@
       <c r="O276" s="44" t="n"/>
       <c r="P276" s="44" t="n"/>
       <c r="Q276" s="44" t="n"/>
+      <c r="R276" s="44" t="n"/>
+      <c r="S276" s="44" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="44" t="n"/>
@@ -10048,6 +10308,8 @@
       <c r="O277" s="44" t="n"/>
       <c r="P277" s="44" t="n"/>
       <c r="Q277" s="44" t="n"/>
+      <c r="R277" s="44" t="n"/>
+      <c r="S277" s="44" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="44" t="n"/>
@@ -10067,6 +10329,8 @@
       <c r="O278" s="44" t="n"/>
       <c r="P278" s="44" t="n"/>
       <c r="Q278" s="44" t="n"/>
+      <c r="R278" s="44" t="n"/>
+      <c r="S278" s="44" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="44" t="n"/>
@@ -10086,6 +10350,8 @@
       <c r="O279" s="44" t="n"/>
       <c r="P279" s="44" t="n"/>
       <c r="Q279" s="44" t="n"/>
+      <c r="R279" s="44" t="n"/>
+      <c r="S279" s="44" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="44" t="n"/>
@@ -10105,6 +10371,8 @@
       <c r="O280" s="44" t="n"/>
       <c r="P280" s="44" t="n"/>
       <c r="Q280" s="44" t="n"/>
+      <c r="R280" s="44" t="n"/>
+      <c r="S280" s="44" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="44" t="n"/>
@@ -10124,6 +10392,8 @@
       <c r="O281" s="44" t="n"/>
       <c r="P281" s="44" t="n"/>
       <c r="Q281" s="44" t="n"/>
+      <c r="R281" s="44" t="n"/>
+      <c r="S281" s="44" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="44" t="n"/>
@@ -10143,6 +10413,8 @@
       <c r="O282" s="44" t="n"/>
       <c r="P282" s="44" t="n"/>
       <c r="Q282" s="44" t="n"/>
+      <c r="R282" s="44" t="n"/>
+      <c r="S282" s="44" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="44" t="n"/>
@@ -10162,6 +10434,8 @@
       <c r="O283" s="44" t="n"/>
       <c r="P283" s="44" t="n"/>
       <c r="Q283" s="44" t="n"/>
+      <c r="R283" s="44" t="n"/>
+      <c r="S283" s="44" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="44" t="n"/>
@@ -10181,6 +10455,8 @@
       <c r="O284" s="44" t="n"/>
       <c r="P284" s="44" t="n"/>
       <c r="Q284" s="44" t="n"/>
+      <c r="R284" s="44" t="n"/>
+      <c r="S284" s="44" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="44" t="n"/>
@@ -10200,6 +10476,8 @@
       <c r="O285" s="44" t="n"/>
       <c r="P285" s="44" t="n"/>
       <c r="Q285" s="44" t="n"/>
+      <c r="R285" s="44" t="n"/>
+      <c r="S285" s="44" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="44" t="n"/>
@@ -10219,6 +10497,8 @@
       <c r="O286" s="44" t="n"/>
       <c r="P286" s="44" t="n"/>
       <c r="Q286" s="44" t="n"/>
+      <c r="R286" s="44" t="n"/>
+      <c r="S286" s="44" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="44" t="n"/>
@@ -10238,6 +10518,8 @@
       <c r="O287" s="44" t="n"/>
       <c r="P287" s="44" t="n"/>
       <c r="Q287" s="44" t="n"/>
+      <c r="R287" s="44" t="n"/>
+      <c r="S287" s="44" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="44" t="n"/>
@@ -10257,6 +10539,8 @@
       <c r="O288" s="44" t="n"/>
       <c r="P288" s="44" t="n"/>
       <c r="Q288" s="44" t="n"/>
+      <c r="R288" s="44" t="n"/>
+      <c r="S288" s="44" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="44" t="n"/>
@@ -10276,6 +10560,8 @@
       <c r="O289" s="44" t="n"/>
       <c r="P289" s="44" t="n"/>
       <c r="Q289" s="44" t="n"/>
+      <c r="R289" s="44" t="n"/>
+      <c r="S289" s="44" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="44" t="n"/>
@@ -10295,6 +10581,8 @@
       <c r="O290" s="44" t="n"/>
       <c r="P290" s="44" t="n"/>
       <c r="Q290" s="44" t="n"/>
+      <c r="R290" s="44" t="n"/>
+      <c r="S290" s="44" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="44" t="n"/>
@@ -10314,6 +10602,8 @@
       <c r="O291" s="44" t="n"/>
       <c r="P291" s="44" t="n"/>
       <c r="Q291" s="44" t="n"/>
+      <c r="R291" s="44" t="n"/>
+      <c r="S291" s="44" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="44" t="n"/>
@@ -10333,6 +10623,8 @@
       <c r="O292" s="44" t="n"/>
       <c r="P292" s="44" t="n"/>
       <c r="Q292" s="44" t="n"/>
+      <c r="R292" s="44" t="n"/>
+      <c r="S292" s="44" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="44" t="n"/>
@@ -10352,6 +10644,8 @@
       <c r="O293" s="44" t="n"/>
       <c r="P293" s="44" t="n"/>
       <c r="Q293" s="44" t="n"/>
+      <c r="R293" s="44" t="n"/>
+      <c r="S293" s="44" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="44" t="n"/>
@@ -10371,6 +10665,8 @@
       <c r="O294" s="44" t="n"/>
       <c r="P294" s="44" t="n"/>
       <c r="Q294" s="44" t="n"/>
+      <c r="R294" s="44" t="n"/>
+      <c r="S294" s="44" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="44" t="n"/>
@@ -10390,6 +10686,8 @@
       <c r="O295" s="44" t="n"/>
       <c r="P295" s="44" t="n"/>
       <c r="Q295" s="44" t="n"/>
+      <c r="R295" s="44" t="n"/>
+      <c r="S295" s="44" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="44" t="n"/>
@@ -10409,6 +10707,8 @@
       <c r="O296" s="44" t="n"/>
       <c r="P296" s="44" t="n"/>
       <c r="Q296" s="44" t="n"/>
+      <c r="R296" s="44" t="n"/>
+      <c r="S296" s="44" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="44" t="n"/>
@@ -10428,6 +10728,8 @@
       <c r="O297" s="44" t="n"/>
       <c r="P297" s="44" t="n"/>
       <c r="Q297" s="44" t="n"/>
+      <c r="R297" s="44" t="n"/>
+      <c r="S297" s="44" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="44" t="n"/>
@@ -10447,6 +10749,8 @@
       <c r="O298" s="44" t="n"/>
       <c r="P298" s="44" t="n"/>
       <c r="Q298" s="44" t="n"/>
+      <c r="R298" s="44" t="n"/>
+      <c r="S298" s="44" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="44" t="n"/>
@@ -10466,6 +10770,8 @@
       <c r="O299" s="44" t="n"/>
       <c r="P299" s="44" t="n"/>
       <c r="Q299" s="44" t="n"/>
+      <c r="R299" s="44" t="n"/>
+      <c r="S299" s="44" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="44" t="n"/>
@@ -10485,6 +10791,8 @@
       <c r="O300" s="44" t="n"/>
       <c r="P300" s="44" t="n"/>
       <c r="Q300" s="44" t="n"/>
+      <c r="R300" s="44" t="n"/>
+      <c r="S300" s="44" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="44" t="n"/>
@@ -10504,6 +10812,8 @@
       <c r="O301" s="44" t="n"/>
       <c r="P301" s="44" t="n"/>
       <c r="Q301" s="44" t="n"/>
+      <c r="R301" s="44" t="n"/>
+      <c r="S301" s="44" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="44" t="n"/>
@@ -10523,6 +10833,8 @@
       <c r="O302" s="44" t="n"/>
       <c r="P302" s="44" t="n"/>
       <c r="Q302" s="44" t="n"/>
+      <c r="R302" s="44" t="n"/>
+      <c r="S302" s="44" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="44" t="n"/>
@@ -10542,6 +10854,8 @@
       <c r="O303" s="44" t="n"/>
       <c r="P303" s="44" t="n"/>
       <c r="Q303" s="44" t="n"/>
+      <c r="R303" s="44" t="n"/>
+      <c r="S303" s="44" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="44" t="n"/>
@@ -10561,6 +10875,8 @@
       <c r="O304" s="44" t="n"/>
       <c r="P304" s="44" t="n"/>
       <c r="Q304" s="44" t="n"/>
+      <c r="R304" s="44" t="n"/>
+      <c r="S304" s="44" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="44" t="n"/>
@@ -10580,6 +10896,8 @@
       <c r="O305" s="44" t="n"/>
       <c r="P305" s="44" t="n"/>
       <c r="Q305" s="44" t="n"/>
+      <c r="R305" s="44" t="n"/>
+      <c r="S305" s="44" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="44" t="n"/>
@@ -14382,10 +14700,24 @@
       <c r="Q505" s="44" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A4:Q4"/>
+  <mergeCells count="17">
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A21:L21"/>
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A30:L30"/>
+    <mergeCell ref="A24:L24"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A33:J33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14420,7 +14752,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="45" t="inlineStr">
         <is>
-          <t>Last run: 2026-04-12  19:56   |   ✓  All OK   |   12 mech + 12 opt = 24 sets   |   Total cost: $3,960,000</t>
+          <t>Last run: 2026-04-13  07:22   |   ✓  All OK   |   12 mech + 12 opt = 24 sets   |   Total cost: $3,960,000</t>
         </is>
       </c>
       <c r="B2" s="24" t="n"/>

--- a/Solver.xlsx
+++ b/Solver.xlsx
@@ -26,7 +26,7 @@
     <numFmt numFmtId="165" formatCode="$#,##0"/>
     <numFmt numFmtId="166" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -135,8 +135,33 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F1F1F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -186,6 +211,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -259,7 +289,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -467,6 +497,41 @@
     <xf numFmtId="165" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="20" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4063,10 +4128,10 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
@@ -4103,7 +4168,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="55" t="inlineStr">
         <is>
-          <t>Last run: 2026-04-13  07:22   |   ✓  All checks passed   |   7 lines used   |   12 mech + 12 opt = 24 tooling sets</t>
+          <t>Last run: 2026-04-13  08:21   |   ✓  All checks passed   |   7 lines used   |   12 mech + 12 opt = 24 tooling sets</t>
         </is>
       </c>
       <c r="B2" s="24" t="n"/>
@@ -5292,18 +5357,22 @@
       <c r="R38" s="44" t="n"/>
       <c r="S38" s="44" t="n"/>
     </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="73" t="n"/>
-      <c r="B39" s="61" t="n"/>
-      <c r="C39" s="61" t="n"/>
-      <c r="D39" s="62" t="n"/>
-      <c r="E39" s="63" t="n"/>
-      <c r="F39" s="63" t="n"/>
-      <c r="G39" s="63" t="n"/>
-      <c r="H39" s="63" t="n"/>
-      <c r="I39" s="63" t="n"/>
-      <c r="J39" s="63" t="n"/>
-      <c r="K39" s="63" t="n"/>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="81" t="inlineStr">
+        <is>
+          <t>7-DAY WORKING CHECK  —  Alternative to opening L6</t>
+        </is>
+      </c>
+      <c r="B39" s="24" t="n"/>
+      <c r="C39" s="24" t="n"/>
+      <c r="D39" s="24" t="n"/>
+      <c r="E39" s="24" t="n"/>
+      <c r="F39" s="24" t="n"/>
+      <c r="G39" s="24" t="n"/>
+      <c r="H39" s="24" t="n"/>
+      <c r="I39" s="24" t="n"/>
+      <c r="J39" s="24" t="n"/>
+      <c r="K39" s="25" t="n"/>
       <c r="L39" s="63" t="n"/>
       <c r="M39" s="63" t="n"/>
       <c r="N39" s="63" t="n"/>
@@ -5313,18 +5382,22 @@
       <c r="R39" s="44" t="n"/>
       <c r="S39" s="44" t="n"/>
     </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="73" t="n"/>
-      <c r="B40" s="61" t="n"/>
-      <c r="C40" s="61" t="n"/>
-      <c r="D40" s="62" t="n"/>
-      <c r="E40" s="63" t="n"/>
-      <c r="F40" s="63" t="n"/>
-      <c r="G40" s="63" t="n"/>
-      <c r="H40" s="63" t="n"/>
-      <c r="I40" s="63" t="n"/>
-      <c r="J40" s="63" t="n"/>
-      <c r="K40" s="63" t="n"/>
+    <row r="40" ht="14" customHeight="1">
+      <c r="A40" s="74" t="inlineStr">
+        <is>
+          <t>From 2035 onward: could the 6 existing line(s) have avoided L6 by working 7 days/week?  (current schedule: 6 days/week)</t>
+        </is>
+      </c>
+      <c r="B40" s="24" t="n"/>
+      <c r="C40" s="24" t="n"/>
+      <c r="D40" s="24" t="n"/>
+      <c r="E40" s="24" t="n"/>
+      <c r="F40" s="24" t="n"/>
+      <c r="G40" s="24" t="n"/>
+      <c r="H40" s="24" t="n"/>
+      <c r="I40" s="24" t="n"/>
+      <c r="J40" s="24" t="n"/>
+      <c r="K40" s="25" t="n"/>
       <c r="L40" s="63" t="n"/>
       <c r="M40" s="63" t="n"/>
       <c r="N40" s="63" t="n"/>
@@ -5334,7 +5407,7 @@
       <c r="R40" s="44" t="n"/>
       <c r="S40" s="44" t="n"/>
     </row>
-    <row r="41" ht="15" customHeight="1">
+    <row r="41" ht="6" customHeight="1">
       <c r="A41" s="73" t="n"/>
       <c r="B41" s="61" t="n"/>
       <c r="C41" s="61" t="n"/>
@@ -5355,18 +5428,65 @@
       <c r="R41" s="44" t="n"/>
       <c r="S41" s="44" t="n"/>
     </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="73" t="n"/>
-      <c r="B42" s="61" t="n"/>
-      <c r="C42" s="61" t="n"/>
-      <c r="D42" s="62" t="n"/>
-      <c r="E42" s="63" t="n"/>
-      <c r="F42" s="63" t="n"/>
-      <c r="G42" s="63" t="n"/>
-      <c r="H42" s="63" t="n"/>
-      <c r="I42" s="63" t="n"/>
-      <c r="J42" s="63" t="n"/>
-      <c r="K42" s="63" t="n"/>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="82" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B42" s="82" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C42" s="82" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D42" s="82" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="E42" s="83" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="F42" s="83" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="G42" s="83" t="inlineStr">
+        <is>
+          <t>L14</t>
+        </is>
+      </c>
+      <c r="H42" s="83" t="inlineStr">
+        <is>
+          <t>Lines
+at 7-day</t>
+        </is>
+      </c>
+      <c r="I42" s="83" t="inlineStr">
+        <is>
+          <t>Total
+Demand</t>
+        </is>
+      </c>
+      <c r="J42" s="83" t="inlineStr">
+        <is>
+          <t>Capacity
+(scenario)</t>
+        </is>
+      </c>
+      <c r="K42" s="83" t="inlineStr">
+        <is>
+          <t>Util %</t>
+        </is>
+      </c>
       <c r="L42" s="63" t="n"/>
       <c r="M42" s="63" t="n"/>
       <c r="N42" s="63" t="n"/>
@@ -5376,18 +5496,52 @@
       <c r="R42" s="44" t="n"/>
       <c r="S42" s="44" t="n"/>
     </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="73" t="n"/>
-      <c r="B43" s="61" t="n"/>
-      <c r="C43" s="61" t="n"/>
-      <c r="D43" s="62" t="n"/>
-      <c r="E43" s="63" t="n"/>
-      <c r="F43" s="63" t="n"/>
-      <c r="G43" s="63" t="n"/>
-      <c r="H43" s="63" t="n"/>
-      <c r="I43" s="63" t="n"/>
-      <c r="J43" s="63" t="n"/>
-      <c r="K43" s="63" t="n"/>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="59" t="n">
+        <v>2035</v>
+      </c>
+      <c r="B43" s="84" t="inlineStr">
+        <is>
+          <t>7d  P2</t>
+        </is>
+      </c>
+      <c r="C43" s="84" t="inlineStr">
+        <is>
+          <t>7d  P2, P4</t>
+        </is>
+      </c>
+      <c r="D43" s="84" t="inlineStr">
+        <is>
+          <t>7d  P2</t>
+        </is>
+      </c>
+      <c r="E43" s="85" t="inlineStr">
+        <is>
+          <t>7d  P2</t>
+        </is>
+      </c>
+      <c r="F43" s="85" t="inlineStr">
+        <is>
+          <t>7d  P1</t>
+        </is>
+      </c>
+      <c r="G43" s="85" t="inlineStr">
+        <is>
+          <t>7d  P2</t>
+        </is>
+      </c>
+      <c r="H43" s="86" t="n">
+        <v>6</v>
+      </c>
+      <c r="I43" s="86" t="n">
+        <v>9370879</v>
+      </c>
+      <c r="J43" s="86" t="n">
+        <v>11038809</v>
+      </c>
+      <c r="K43" s="87" t="n">
+        <v>84.90000000000001</v>
+      </c>
       <c r="L43" s="63" t="n"/>
       <c r="M43" s="63" t="n"/>
       <c r="N43" s="63" t="n"/>
@@ -5397,18 +5551,52 @@
       <c r="R43" s="44" t="n"/>
       <c r="S43" s="44" t="n"/>
     </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="73" t="n"/>
-      <c r="B44" s="61" t="n"/>
-      <c r="C44" s="61" t="n"/>
-      <c r="D44" s="62" t="n"/>
-      <c r="E44" s="63" t="n"/>
-      <c r="F44" s="63" t="n"/>
-      <c r="G44" s="63" t="n"/>
-      <c r="H44" s="63" t="n"/>
-      <c r="I44" s="63" t="n"/>
-      <c r="J44" s="63" t="n"/>
-      <c r="K44" s="63" t="n"/>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="59" t="n">
+        <v>2036</v>
+      </c>
+      <c r="B44" s="84" t="inlineStr">
+        <is>
+          <t>7d  P2</t>
+        </is>
+      </c>
+      <c r="C44" s="84" t="inlineStr">
+        <is>
+          <t>7d  P4</t>
+        </is>
+      </c>
+      <c r="D44" s="84" t="inlineStr">
+        <is>
+          <t>7d  P2</t>
+        </is>
+      </c>
+      <c r="E44" s="85" t="inlineStr">
+        <is>
+          <t>7d  P2</t>
+        </is>
+      </c>
+      <c r="F44" s="85" t="inlineStr">
+        <is>
+          <t>7d  P1</t>
+        </is>
+      </c>
+      <c r="G44" s="88" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H44" s="86" t="n">
+        <v>5</v>
+      </c>
+      <c r="I44" s="86" t="n">
+        <v>9277824</v>
+      </c>
+      <c r="J44" s="86" t="n">
+        <v>10839744</v>
+      </c>
+      <c r="K44" s="87" t="n">
+        <v>85.59999999999999</v>
+      </c>
       <c r="L44" s="63" t="n"/>
       <c r="M44" s="63" t="n"/>
       <c r="N44" s="63" t="n"/>
@@ -5418,18 +5606,52 @@
       <c r="R44" s="44" t="n"/>
       <c r="S44" s="44" t="n"/>
     </row>
-    <row r="45">
-      <c r="A45" s="44" t="n"/>
-      <c r="B45" s="44" t="n"/>
-      <c r="C45" s="44" t="n"/>
-      <c r="D45" s="44" t="n"/>
-      <c r="E45" s="44" t="n"/>
-      <c r="F45" s="44" t="n"/>
-      <c r="G45" s="44" t="n"/>
-      <c r="H45" s="44" t="n"/>
-      <c r="I45" s="44" t="n"/>
-      <c r="J45" s="44" t="n"/>
-      <c r="K45" s="44" t="n"/>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="59" t="n">
+        <v>2037</v>
+      </c>
+      <c r="B45" s="84" t="inlineStr">
+        <is>
+          <t>7d  P4</t>
+        </is>
+      </c>
+      <c r="C45" s="89" t="inlineStr">
+        <is>
+          <t>7d —</t>
+        </is>
+      </c>
+      <c r="D45" s="84" t="inlineStr">
+        <is>
+          <t>7d  P2</t>
+        </is>
+      </c>
+      <c r="E45" s="90" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F45" s="90" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G45" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H45" s="91" t="n">
+        <v>3</v>
+      </c>
+      <c r="I45" s="86" t="n">
+        <v>4271659</v>
+      </c>
+      <c r="J45" s="86" t="n">
+        <v>10310976</v>
+      </c>
+      <c r="K45" s="87" t="n">
+        <v>41.4</v>
+      </c>
       <c r="L45" s="44" t="n"/>
       <c r="M45" s="44" t="n"/>
       <c r="N45" s="44" t="n"/>
@@ -5439,18 +5661,52 @@
       <c r="R45" s="44" t="n"/>
       <c r="S45" s="44" t="n"/>
     </row>
-    <row r="46">
-      <c r="A46" s="44" t="n"/>
-      <c r="B46" s="44" t="n"/>
-      <c r="C46" s="44" t="n"/>
-      <c r="D46" s="44" t="n"/>
-      <c r="E46" s="44" t="n"/>
-      <c r="F46" s="44" t="n"/>
-      <c r="G46" s="44" t="n"/>
-      <c r="H46" s="44" t="n"/>
-      <c r="I46" s="44" t="n"/>
-      <c r="J46" s="44" t="n"/>
-      <c r="K46" s="44" t="n"/>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="59" t="n">
+        <v>2038</v>
+      </c>
+      <c r="B46" s="84" t="inlineStr">
+        <is>
+          <t>7d  P4</t>
+        </is>
+      </c>
+      <c r="C46" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D46" s="90" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E46" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F46" s="90" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G46" s="71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H46" s="91" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="86" t="n">
+        <v>1216264</v>
+      </c>
+      <c r="J46" s="86" t="n">
+        <v>9782208</v>
+      </c>
+      <c r="K46" s="87" t="n">
+        <v>12.4</v>
+      </c>
       <c r="L46" s="44" t="n"/>
       <c r="M46" s="44" t="n"/>
       <c r="N46" s="44" t="n"/>
@@ -5481,10 +5737,14 @@
       <c r="R47" s="44" t="n"/>
       <c r="S47" s="44" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="14" customHeight="1">
       <c r="A48" s="44" t="n"/>
-      <c r="B48" s="44" t="n"/>
-      <c r="C48" s="44" t="n"/>
+      <c r="B48" s="92" t="inlineStr"/>
+      <c r="C48" s="55" t="inlineStr">
+        <is>
+          <t>Line must work 7 days/week to absorb demand from removed line</t>
+        </is>
+      </c>
       <c r="D48" s="44" t="n"/>
       <c r="E48" s="44" t="n"/>
       <c r="F48" s="44" t="n"/>
@@ -5502,10 +5762,14 @@
       <c r="R48" s="44" t="n"/>
       <c r="S48" s="44" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="14" customHeight="1">
       <c r="A49" s="44" t="n"/>
-      <c r="B49" s="44" t="n"/>
-      <c r="C49" s="44" t="n"/>
+      <c r="B49" s="29" t="inlineStr"/>
+      <c r="C49" s="55" t="inlineStr">
+        <is>
+          <t>Line at normal 6 days/week — single product</t>
+        </is>
+      </c>
       <c r="D49" s="44" t="n"/>
       <c r="E49" s="44" t="n"/>
       <c r="F49" s="44" t="n"/>
@@ -5523,10 +5787,14 @@
       <c r="R49" s="44" t="n"/>
       <c r="S49" s="44" t="n"/>
     </row>
-    <row r="50">
+    <row r="50" ht="14" customHeight="1">
       <c r="A50" s="44" t="n"/>
-      <c r="B50" s="44" t="n"/>
-      <c r="C50" s="44" t="n"/>
+      <c r="B50" s="93" t="inlineStr"/>
+      <c r="C50" s="55" t="inlineStr">
+        <is>
+          <t>Line at normal 6 days/week — multi product</t>
+        </is>
+      </c>
       <c r="D50" s="44" t="n"/>
       <c r="E50" s="44" t="n"/>
       <c r="F50" s="44" t="n"/>
@@ -14700,10 +14968,11 @@
       <c r="Q505" s="44" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="19">
     <mergeCell ref="A32:J32"/>
     <mergeCell ref="A36:J36"/>
     <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A39:K39"/>
     <mergeCell ref="A28:L28"/>
     <mergeCell ref="A35:J35"/>
     <mergeCell ref="A27:L27"/>
@@ -14717,6 +14986,7 @@
     <mergeCell ref="A23:L23"/>
     <mergeCell ref="A34:J34"/>
     <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A40:K40"/>
     <mergeCell ref="A33:J33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14752,7 +15022,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="45" t="inlineStr">
         <is>
-          <t>Last run: 2026-04-13  07:22   |   ✓  All OK   |   12 mech + 12 opt = 24 sets   |   Total cost: $3,960,000</t>
+          <t>Last run: 2026-04-13  08:21   |   ✓  All OK   |   12 mech + 12 opt = 24 sets   |   Total cost: $3,960,000</t>
         </is>
       </c>
       <c r="B2" s="24" t="n"/>
